--- a/research/traditional_assets/database/data/bahrain/bahrain_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_real_estate_general_diversified.xlsx
@@ -1264,43 +1264,43 @@
         <v>7.31718061674009</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>199.04682813307</v>
       </c>
       <c r="G2">
         <v>1.43715846994536</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.090655737704918</v>
       </c>
       <c r="I2">
         <v>0.158529234478602</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>139.6</v>
       </c>
       <c r="L2">
-        <v>183.261804019128</v>
+        <v>181.520701524186</v>
       </c>
       <c r="M2">
         <v>160.79</v>
       </c>
       <c r="N2">
-        <v>178.151804019128</v>
+        <v>178.069701524186</v>
       </c>
       <c r="O2">
         <v>26.3</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.659</v>
       </c>
       <c r="Q2">
         <v>0.117863129814636</v>
       </c>
       <c r="R2">
-        <v>0.107324552059416</v>
+        <v>0.107369552059416</v>
       </c>
       <c r="S2">
         <v>0.112277188197372</v>
@@ -1322,13 +1322,13 @@
         <v>0.118915495606427</v>
       </c>
       <c r="X2">
-        <v>0.107324552059416</v>
+        <v>0.107946012181229</v>
       </c>
       <c r="Y2">
         <v>0.626291522444978</v>
       </c>
       <c r="Z2">
-        <v>0.527006006831337</v>
+        <v>0.532329299829634</v>
       </c>
       <c r="AA2">
         <v>26.3</v>
@@ -1409,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1546,22 +1546,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1073245520594164</v>
+        <v>0.1073695520594164</v>
       </c>
       <c r="C2">
-        <v>183.2618040191284</v>
+        <v>181.5207015241858</v>
       </c>
       <c r="D2">
-        <v>178.1518040191284</v>
+        <v>178.0697015241857</v>
       </c>
       <c r="E2">
-        <v>-26.3</v>
+        <v>-24.641</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.659</v>
       </c>
       <c r="G2">
         <v>5.11</v>
@@ -1582,28 +1582,28 @@
         <v>16.61</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0834477</v>
       </c>
       <c r="N2">
-        <v>16.61</v>
+        <v>16.5265523</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>16.61</v>
+        <v>16.5265523</v>
       </c>
       <c r="Q2">
-        <v>18.3</v>
+        <v>18.2165523</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1073245520594164</v>
+        <v>0.1079460121812286</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313374</v>
+        <v>0.5323292998296337</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>199.0468281330702</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1628,22 +1628,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1073695520594164</v>
+        <v>0.1074145520594164</v>
       </c>
       <c r="C3">
-        <v>181.5207015241858</v>
+        <v>179.7796746693927</v>
       </c>
       <c r="D3">
-        <v>178.0697015241857</v>
+        <v>177.9876746693927</v>
       </c>
       <c r="E3">
-        <v>-24.641</v>
+        <v>-22.982</v>
       </c>
       <c r="F3">
-        <v>1.659</v>
+        <v>3.318</v>
       </c>
       <c r="G3">
         <v>5.11</v>
@@ -1664,28 +1664,28 @@
         <v>16.61</v>
       </c>
       <c r="M3">
-        <v>0.0834477</v>
+        <v>0.1668954</v>
       </c>
       <c r="N3">
-        <v>16.5265523</v>
+        <v>16.4431046</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>16.5265523</v>
+        <v>16.4431046</v>
       </c>
       <c r="Q3">
-        <v>18.2165523</v>
+        <v>18.1331046</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1079460121812286</v>
+        <v>0.1085801551626698</v>
       </c>
       <c r="T3">
-        <v>0.5323292998296337</v>
+        <v>0.5377612314605483</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>199.0468281330702</v>
+        <v>99.52341406653508</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1710,22 +1710,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1074145520594164</v>
+        <v>0.1074595520594163</v>
       </c>
       <c r="C4">
-        <v>179.7796746693927</v>
+        <v>178.0387233502677</v>
       </c>
       <c r="D4">
-        <v>177.9876746693927</v>
+        <v>177.9057233502677</v>
       </c>
       <c r="E4">
-        <v>-22.982</v>
+        <v>-21.323</v>
       </c>
       <c r="F4">
-        <v>3.318</v>
+        <v>4.977</v>
       </c>
       <c r="G4">
         <v>5.11</v>
@@ -1746,28 +1746,28 @@
         <v>16.61</v>
       </c>
       <c r="M4">
-        <v>0.1668954</v>
+        <v>0.2503431</v>
       </c>
       <c r="N4">
-        <v>16.4431046</v>
+        <v>16.3596569</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>16.4431046</v>
+        <v>16.3596569</v>
       </c>
       <c r="Q4">
-        <v>18.1331046</v>
+        <v>18.0496569</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1085801551626698</v>
+        <v>0.1092273732571303</v>
       </c>
       <c r="T4">
-        <v>0.5377612314605483</v>
+        <v>0.543305161681791</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>99.52341406653508</v>
+        <v>66.3489427110234</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1792,22 +1792,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1074595520594163</v>
+        <v>0.1075045520594163</v>
       </c>
       <c r="C5">
-        <v>178.0387233502677</v>
+        <v>176.2978474625214</v>
       </c>
       <c r="D5">
-        <v>177.9057233502677</v>
+        <v>177.8238474625214</v>
       </c>
       <c r="E5">
-        <v>-21.323</v>
+        <v>-19.664</v>
       </c>
       <c r="F5">
-        <v>4.977</v>
+        <v>6.636</v>
       </c>
       <c r="G5">
         <v>5.11</v>
@@ -1828,28 +1828,28 @@
         <v>16.61</v>
       </c>
       <c r="M5">
-        <v>0.2503431</v>
+        <v>0.3337908</v>
       </c>
       <c r="N5">
-        <v>16.3596569</v>
+        <v>16.2762092</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>16.3596569</v>
+        <v>16.2762092</v>
       </c>
       <c r="Q5">
-        <v>18.0496569</v>
+        <v>17.9662092</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1092273732571303</v>
+        <v>0.109888075061892</v>
       </c>
       <c r="T5">
-        <v>0.543305161681791</v>
+        <v>0.5489645904493098</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>66.3489427110234</v>
+        <v>49.76170703326754</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1874,22 +1874,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1075045520594163</v>
+        <v>0.1075495520594163</v>
       </c>
       <c r="C6">
-        <v>176.2978474625214</v>
+        <v>174.5570469020567</v>
       </c>
       <c r="D6">
-        <v>177.8238474625214</v>
+        <v>177.7420469020567</v>
       </c>
       <c r="E6">
-        <v>-19.664</v>
+        <v>-18.005</v>
       </c>
       <c r="F6">
-        <v>6.636</v>
+        <v>8.295</v>
       </c>
       <c r="G6">
         <v>5.11</v>
@@ -1910,28 +1910,28 @@
         <v>16.61</v>
       </c>
       <c r="M6">
-        <v>0.3337908</v>
+        <v>0.4172385</v>
       </c>
       <c r="N6">
-        <v>16.2762092</v>
+        <v>16.1927615</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>16.2762092</v>
+        <v>16.1927615</v>
       </c>
       <c r="Q6">
-        <v>17.9662092</v>
+        <v>17.8827615</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.109888075061892</v>
+        <v>0.110562686378333</v>
       </c>
       <c r="T6">
-        <v>0.5489645904493098</v>
+        <v>0.5547431650856183</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.76170703326754</v>
+        <v>39.80936562661404</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1956,22 +1956,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1075495520594163</v>
+        <v>0.1075945520594163</v>
       </c>
       <c r="C7">
-        <v>174.5570469020567</v>
+        <v>172.8163215649676</v>
       </c>
       <c r="D7">
-        <v>177.7420469020567</v>
+        <v>177.6603215649675</v>
       </c>
       <c r="E7">
-        <v>-18.005</v>
+        <v>-16.346</v>
       </c>
       <c r="F7">
-        <v>8.295</v>
+        <v>9.954000000000001</v>
       </c>
       <c r="G7">
         <v>5.11</v>
@@ -1992,28 +1992,28 @@
         <v>16.61</v>
       </c>
       <c r="M7">
-        <v>0.4172385</v>
+        <v>0.5006862</v>
       </c>
       <c r="N7">
-        <v>16.1927615</v>
+        <v>16.1093138</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>16.1927615</v>
+        <v>16.1093138</v>
       </c>
       <c r="Q7">
-        <v>17.8827615</v>
+        <v>17.7993138</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.110562686378333</v>
+        <v>0.1112516511270387</v>
       </c>
       <c r="T7">
-        <v>0.5547431650856183</v>
+        <v>0.560644688118444</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.80936562661404</v>
+        <v>33.1744713555117</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2038,22 +2038,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1075945520594163</v>
+        <v>0.1076395520594163</v>
       </c>
       <c r="C8">
-        <v>172.8163215649676</v>
+        <v>171.0756713475392</v>
       </c>
       <c r="D8">
-        <v>177.6603215649675</v>
+        <v>177.5786713475392</v>
       </c>
       <c r="E8">
-        <v>-16.346</v>
+        <v>-14.687</v>
       </c>
       <c r="F8">
-        <v>9.954000000000001</v>
+        <v>11.613</v>
       </c>
       <c r="G8">
         <v>5.11</v>
@@ -2074,28 +2074,28 @@
         <v>16.61</v>
       </c>
       <c r="M8">
-        <v>0.5006862</v>
+        <v>0.5841339</v>
       </c>
       <c r="N8">
-        <v>16.1093138</v>
+        <v>16.0258661</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>16.1093138</v>
+        <v>16.0258661</v>
       </c>
       <c r="Q8">
-        <v>17.7993138</v>
+        <v>17.7158661</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1112516511270387</v>
+        <v>0.111955432321953</v>
       </c>
       <c r="T8">
-        <v>0.560644688118444</v>
+        <v>0.5666731256250939</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.1744713555117</v>
+        <v>28.43526116186716</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2120,22 +2120,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1076395520594163</v>
+        <v>0.1076845520594164</v>
       </c>
       <c r="C9">
-        <v>171.0756713475392</v>
+        <v>169.3350961462472</v>
       </c>
       <c r="D9">
-        <v>177.5786713475392</v>
+        <v>177.4970961462472</v>
       </c>
       <c r="E9">
-        <v>-14.687</v>
+        <v>-13.028</v>
       </c>
       <c r="F9">
-        <v>11.613</v>
+        <v>13.272</v>
       </c>
       <c r="G9">
         <v>5.11</v>
@@ -2156,28 +2156,28 @@
         <v>16.61</v>
       </c>
       <c r="M9">
-        <v>0.5841339</v>
+        <v>0.6675816</v>
       </c>
       <c r="N9">
-        <v>16.0258661</v>
+        <v>15.9424184</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>16.0258661</v>
+        <v>15.9424184</v>
       </c>
       <c r="Q9">
-        <v>17.7158661</v>
+        <v>17.6324184</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.111955432321953</v>
+        <v>0.1126745131080613</v>
       </c>
       <c r="T9">
-        <v>0.5666731256250939</v>
+        <v>0.5728326161210189</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.43526116186716</v>
+        <v>24.88085351663377</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2202,22 +2202,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1076845520594164</v>
+        <v>0.1077295520594164</v>
       </c>
       <c r="C10">
-        <v>169.3350961462472</v>
+        <v>167.5945958577577</v>
       </c>
       <c r="D10">
-        <v>177.4970961462472</v>
+        <v>177.4155958577577</v>
       </c>
       <c r="E10">
-        <v>-13.028</v>
+        <v>-11.369</v>
       </c>
       <c r="F10">
-        <v>13.272</v>
+        <v>14.931</v>
       </c>
       <c r="G10">
         <v>5.11</v>
@@ -2238,28 +2238,28 @@
         <v>16.61</v>
       </c>
       <c r="M10">
-        <v>0.6675816</v>
+        <v>0.7510292999999999</v>
       </c>
       <c r="N10">
-        <v>15.9424184</v>
+        <v>15.8589707</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>15.9424184</v>
+        <v>15.8589707</v>
       </c>
       <c r="Q10">
-        <v>17.6324184</v>
+        <v>17.5489707</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1126745131080613</v>
+        <v>0.1134093978674905</v>
       </c>
       <c r="T10">
-        <v>0.5728326161210189</v>
+        <v>0.5791274800344367</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.88085351663377</v>
+        <v>22.1163142370078</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2284,22 +2284,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1077295520594164</v>
+        <v>0.1077745520594164</v>
       </c>
       <c r="C11">
-        <v>167.5945958577577</v>
+        <v>165.854170378926</v>
       </c>
       <c r="D11">
-        <v>177.4155958577577</v>
+        <v>177.334170378926</v>
       </c>
       <c r="E11">
-        <v>-11.369</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="F11">
-        <v>14.931</v>
+        <v>16.59</v>
       </c>
       <c r="G11">
         <v>5.11</v>
@@ -2320,28 +2320,28 @@
         <v>16.61</v>
       </c>
       <c r="M11">
-        <v>0.7510292999999999</v>
+        <v>0.8344769999999999</v>
       </c>
       <c r="N11">
-        <v>15.8589707</v>
+        <v>15.775523</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>15.8589707</v>
+        <v>15.775523</v>
       </c>
       <c r="Q11">
-        <v>17.5489707</v>
+        <v>17.465523</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1134093978674905</v>
+        <v>0.1141606133993515</v>
       </c>
       <c r="T11">
-        <v>0.5791274800344367</v>
+        <v>0.5855622298125971</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.1163142370078</v>
+        <v>19.90468281330702</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1077745520594164</v>
+        <v>0.1078195520594163</v>
       </c>
       <c r="C12">
-        <v>165.854170378926</v>
+        <v>164.113819606797</v>
       </c>
       <c r="D12">
-        <v>177.334170378926</v>
+        <v>177.252819606797</v>
       </c>
       <c r="E12">
-        <v>-9.710000000000001</v>
+        <v>-8.050999999999998</v>
       </c>
       <c r="F12">
-        <v>16.59</v>
+        <v>18.249</v>
       </c>
       <c r="G12">
         <v>5.11</v>
@@ -2402,28 +2402,28 @@
         <v>16.61</v>
       </c>
       <c r="M12">
-        <v>0.8344769999999999</v>
+        <v>0.9179247</v>
       </c>
       <c r="N12">
-        <v>15.775523</v>
+        <v>15.6920753</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>15.775523</v>
+        <v>15.6920753</v>
       </c>
       <c r="Q12">
-        <v>17.465523</v>
+        <v>17.3820753</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1141606133993515</v>
+        <v>0.1149287101791195</v>
       </c>
       <c r="T12">
-        <v>0.5855622298125971</v>
+        <v>0.5921415807093678</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.90468281330702</v>
+        <v>18.09516619391547</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1078195520594163</v>
+        <v>0.1078645520594163</v>
       </c>
       <c r="C13">
-        <v>164.113819606797</v>
+        <v>162.3735434386044</v>
       </c>
       <c r="D13">
-        <v>177.252819606797</v>
+        <v>177.1715434386044</v>
       </c>
       <c r="E13">
-        <v>-8.050999999999998</v>
+        <v>-6.391999999999999</v>
       </c>
       <c r="F13">
-        <v>18.249</v>
+        <v>19.908</v>
       </c>
       <c r="G13">
         <v>5.11</v>
@@ -2484,28 +2484,28 @@
         <v>16.61</v>
       </c>
       <c r="M13">
-        <v>0.9179247</v>
+        <v>1.0013724</v>
       </c>
       <c r="N13">
-        <v>15.6920753</v>
+        <v>15.6086276</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>15.6920753</v>
+        <v>15.6086276</v>
       </c>
       <c r="Q13">
-        <v>17.3820753</v>
+        <v>17.2986276</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1149287101791195</v>
+        <v>0.1157142637038822</v>
       </c>
       <c r="T13">
-        <v>0.5921415807093678</v>
+        <v>0.5988704623083378</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.09516619391547</v>
+        <v>16.58723567775585</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2530,22 +2530,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1078645520594163</v>
+        <v>0.1079095520594163</v>
       </c>
       <c r="C14">
-        <v>162.3735434386044</v>
+        <v>160.6333417717703</v>
       </c>
       <c r="D14">
-        <v>177.1715434386044</v>
+        <v>177.0903417717703</v>
       </c>
       <c r="E14">
-        <v>-6.391999999999999</v>
+        <v>-4.733000000000001</v>
       </c>
       <c r="F14">
-        <v>19.908</v>
+        <v>21.567</v>
       </c>
       <c r="G14">
         <v>5.11</v>
@@ -2566,28 +2566,28 @@
         <v>16.61</v>
       </c>
       <c r="M14">
-        <v>1.0013724</v>
+        <v>1.0848201</v>
       </c>
       <c r="N14">
-        <v>15.6086276</v>
+        <v>15.5251799</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>15.6086276</v>
+        <v>15.5251799</v>
       </c>
       <c r="Q14">
-        <v>17.2986276</v>
+        <v>17.2151799</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1157142637038822</v>
+        <v>0.1165178759303636</v>
       </c>
       <c r="T14">
-        <v>0.5988704623083378</v>
+        <v>0.6057540308406176</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.58723567775585</v>
+        <v>15.31129447177463</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2612,22 +2612,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1079095520594163</v>
+        <v>0.1079545520594164</v>
       </c>
       <c r="C15">
-        <v>160.6333417717703</v>
+        <v>158.8932145039046</v>
       </c>
       <c r="D15">
-        <v>177.0903417717703</v>
+        <v>177.0092145039046</v>
       </c>
       <c r="E15">
-        <v>-4.733000000000001</v>
+        <v>-3.073999999999998</v>
       </c>
       <c r="F15">
-        <v>21.567</v>
+        <v>23.226</v>
       </c>
       <c r="G15">
         <v>5.11</v>
@@ -2648,28 +2648,28 @@
         <v>16.61</v>
       </c>
       <c r="M15">
-        <v>1.0848201</v>
+        <v>1.1682678</v>
       </c>
       <c r="N15">
-        <v>15.5251799</v>
+        <v>15.4417322</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>15.5251799</v>
+        <v>15.4417322</v>
       </c>
       <c r="Q15">
-        <v>17.2151799</v>
+        <v>17.1317322</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1165178759303636</v>
+        <v>0.1173401768132748</v>
       </c>
       <c r="T15">
-        <v>0.6057540308406176</v>
+        <v>0.6127976823620203</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.31129447177463</v>
+        <v>14.21763058093358</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2694,22 +2694,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1079545520594164</v>
+        <v>0.1079995520594163</v>
       </c>
       <c r="C16">
-        <v>158.8932145039046</v>
+        <v>157.153161532805</v>
       </c>
       <c r="D16">
-        <v>177.0092145039046</v>
+        <v>176.9281615328049</v>
       </c>
       <c r="E16">
-        <v>-3.073999999999998</v>
+        <v>-1.414999999999996</v>
       </c>
       <c r="F16">
-        <v>23.226</v>
+        <v>24.88500000000001</v>
       </c>
       <c r="G16">
         <v>5.11</v>
@@ -2730,28 +2730,28 @@
         <v>16.61</v>
       </c>
       <c r="M16">
-        <v>1.1682678</v>
+        <v>1.2517155</v>
       </c>
       <c r="N16">
-        <v>15.4417322</v>
+        <v>15.3582845</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>15.4417322</v>
+        <v>15.3582845</v>
       </c>
       <c r="Q16">
-        <v>17.1317322</v>
+        <v>17.0482845</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1173401768132748</v>
+        <v>0.1181818259522545</v>
       </c>
       <c r="T16">
-        <v>0.6127976823620203</v>
+        <v>0.6200070668603969</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.21763058093358</v>
+        <v>13.26978854220468</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1079995520594163</v>
+        <v>0.1082845520594163</v>
       </c>
       <c r="C17">
-        <v>157.153161532805</v>
+        <v>154.9825448205912</v>
       </c>
       <c r="D17">
-        <v>176.9281615328049</v>
+        <v>176.4165448205912</v>
       </c>
       <c r="E17">
-        <v>-1.414999999999999</v>
+        <v>0.2439999999999998</v>
       </c>
       <c r="F17">
-        <v>24.885</v>
+        <v>26.544</v>
       </c>
       <c r="G17">
         <v>5.11</v>
@@ -2812,45 +2812,45 @@
         <v>16.61</v>
       </c>
       <c r="M17">
-        <v>1.2517155</v>
+        <v>1.3749792</v>
       </c>
       <c r="N17">
-        <v>15.3582845</v>
+        <v>15.2350208</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>15.3582845</v>
+        <v>15.2350208</v>
       </c>
       <c r="Q17">
-        <v>17.0482845</v>
+        <v>16.9250208</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1181818259522545</v>
+        <v>0.119043514356448</v>
       </c>
       <c r="T17">
-        <v>0.6200070668603969</v>
+        <v>0.6273881033706397</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.26978854220468</v>
+        <v>12.08018274021891</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2858,22 +2858,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1082845520594163</v>
+        <v>0.1083445520594163</v>
       </c>
       <c r="C18">
-        <v>154.9825448205912</v>
+        <v>153.2162128372557</v>
       </c>
       <c r="D18">
-        <v>176.4165448205912</v>
+        <v>176.3092128372557</v>
       </c>
       <c r="E18">
-        <v>0.2439999999999998</v>
+        <v>1.903000000000002</v>
       </c>
       <c r="F18">
-        <v>26.544</v>
+        <v>28.203</v>
       </c>
       <c r="G18">
         <v>5.11</v>
@@ -2894,28 +2894,28 @@
         <v>16.61</v>
       </c>
       <c r="M18">
-        <v>1.3749792</v>
+        <v>1.4609154</v>
       </c>
       <c r="N18">
-        <v>15.2350208</v>
+        <v>15.1490846</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>15.2350208</v>
+        <v>15.1490846</v>
       </c>
       <c r="Q18">
-        <v>16.9250208</v>
+        <v>16.8390846</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.119043514356448</v>
+        <v>0.1199259663366462</v>
       </c>
       <c r="T18">
-        <v>0.6273881033706397</v>
+        <v>0.6349469961823342</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.08018274021891</v>
+        <v>11.36958375550014</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2940,22 +2940,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1083445520594163</v>
+        <v>0.1084045520594163</v>
       </c>
       <c r="C19">
-        <v>153.2162128372557</v>
+        <v>151.4500113762593</v>
       </c>
       <c r="D19">
-        <v>176.3092128372557</v>
+        <v>176.2020113762592</v>
       </c>
       <c r="E19">
-        <v>1.903000000000002</v>
+        <v>3.562000000000005</v>
       </c>
       <c r="F19">
-        <v>28.203</v>
+        <v>29.86200000000001</v>
       </c>
       <c r="G19">
         <v>5.11</v>
@@ -2976,28 +2976,28 @@
         <v>16.61</v>
       </c>
       <c r="M19">
-        <v>1.4609154</v>
+        <v>1.5468516</v>
       </c>
       <c r="N19">
-        <v>15.1490846</v>
+        <v>15.0631484</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>15.1490846</v>
+        <v>15.0631484</v>
       </c>
       <c r="Q19">
-        <v>16.8390846</v>
+        <v>16.7531484</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1199259663366462</v>
+        <v>0.1208299415358736</v>
       </c>
       <c r="T19">
-        <v>0.6349469961823342</v>
+        <v>0.6426902522333382</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.36958375550014</v>
+        <v>10.73794021352791</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3022,22 +3022,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1084045520594163</v>
+        <v>0.1084645520594164</v>
       </c>
       <c r="C20">
-        <v>151.4500113762592</v>
+        <v>149.6839401996615</v>
       </c>
       <c r="D20">
-        <v>176.2020113762592</v>
+        <v>176.0949401996616</v>
       </c>
       <c r="E20">
-        <v>3.561999999999998</v>
+        <v>5.221</v>
       </c>
       <c r="F20">
-        <v>29.862</v>
+        <v>31.521</v>
       </c>
       <c r="G20">
         <v>5.11</v>
@@ -3058,28 +3058,28 @@
         <v>16.61</v>
       </c>
       <c r="M20">
-        <v>1.5468516</v>
+        <v>1.6327878</v>
       </c>
       <c r="N20">
-        <v>15.0631484</v>
+        <v>14.9772122</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>15.0631484</v>
+        <v>14.9772122</v>
       </c>
       <c r="Q20">
-        <v>16.7531484</v>
+        <v>16.6672122</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1208299415358736</v>
+        <v>0.1217562371103905</v>
       </c>
       <c r="T20">
-        <v>0.6426902522333382</v>
+        <v>0.6506246997917745</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.73794021352792</v>
+        <v>10.1727854654475</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3104,22 +3104,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1084645520594164</v>
+        <v>0.1088645520594164</v>
       </c>
       <c r="C21">
-        <v>149.6839401996615</v>
+        <v>147.3144443821903</v>
       </c>
       <c r="D21">
-        <v>176.0949401996616</v>
+        <v>175.3844443821903</v>
       </c>
       <c r="E21">
-        <v>5.221</v>
+        <v>6.879999999999999</v>
       </c>
       <c r="F21">
-        <v>31.521</v>
+        <v>33.18</v>
       </c>
       <c r="G21">
         <v>5.11</v>
@@ -3140,45 +3140,45 @@
         <v>16.61</v>
       </c>
       <c r="M21">
-        <v>1.6327878</v>
+        <v>1.77513</v>
       </c>
       <c r="N21">
-        <v>14.9772122</v>
+        <v>14.83487</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>14.9772122</v>
+        <v>14.83487</v>
       </c>
       <c r="Q21">
-        <v>16.6672122</v>
+        <v>16.52487</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1217562371103905</v>
+        <v>0.1227056900742704</v>
       </c>
       <c r="T21">
-        <v>0.6506246997917745</v>
+        <v>0.6587575085391717</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.1727854654475</v>
+        <v>9.357061172984514</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3186,22 +3186,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1088645520594164</v>
+        <v>0.1089415520594164</v>
       </c>
       <c r="C22">
-        <v>147.3144443821903</v>
+        <v>145.5193314863187</v>
       </c>
       <c r="D22">
-        <v>175.3844443821903</v>
+        <v>175.2483314863187</v>
       </c>
       <c r="E22">
-        <v>6.879999999999999</v>
+        <v>8.539000000000005</v>
       </c>
       <c r="F22">
-        <v>33.18</v>
+        <v>34.83900000000001</v>
       </c>
       <c r="G22">
         <v>5.11</v>
@@ -3222,28 +3222,28 @@
         <v>16.61</v>
       </c>
       <c r="M22">
-        <v>1.77513</v>
+        <v>1.8638865</v>
       </c>
       <c r="N22">
-        <v>14.83487</v>
+        <v>14.7461135</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>14.83487</v>
+        <v>14.7461135</v>
       </c>
       <c r="Q22">
-        <v>16.52487</v>
+        <v>16.4361135</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1227056900742704</v>
+        <v>0.123679179822046</v>
       </c>
       <c r="T22">
-        <v>0.6587575085391717</v>
+        <v>0.667096211178908</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.357061172984514</v>
+        <v>8.911486831413821</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3268,22 +3268,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1089415520594164</v>
+        <v>0.1090185520594164</v>
       </c>
       <c r="C23">
-        <v>145.5193314863187</v>
+        <v>143.7244296964362</v>
       </c>
       <c r="D23">
-        <v>175.2483314863187</v>
+        <v>175.1124296964362</v>
       </c>
       <c r="E23">
-        <v>8.538999999999998</v>
+        <v>10.198</v>
       </c>
       <c r="F23">
-        <v>34.839</v>
+        <v>36.498</v>
       </c>
       <c r="G23">
         <v>5.11</v>
@@ -3304,28 +3304,28 @@
         <v>16.61</v>
       </c>
       <c r="M23">
-        <v>1.8638865</v>
+        <v>1.952643</v>
       </c>
       <c r="N23">
-        <v>14.7461135</v>
+        <v>14.657357</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>14.7461135</v>
+        <v>14.657357</v>
       </c>
       <c r="Q23">
-        <v>16.4361135</v>
+        <v>16.347357</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.123679179822046</v>
+        <v>0.1246776308454056</v>
       </c>
       <c r="T23">
-        <v>0.667096211178908</v>
+        <v>0.6756487267068427</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.911486831413823</v>
+        <v>8.506419248167738</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3350,22 +3350,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1090185520594164</v>
+        <v>0.1090955520594163</v>
       </c>
       <c r="C24">
-        <v>143.7244296964362</v>
+        <v>141.929738521797</v>
       </c>
       <c r="D24">
-        <v>175.1124296964362</v>
+        <v>174.976738521797</v>
       </c>
       <c r="E24">
-        <v>10.198</v>
+        <v>11.857</v>
       </c>
       <c r="F24">
-        <v>36.498</v>
+        <v>38.157</v>
       </c>
       <c r="G24">
         <v>5.11</v>
@@ -3386,28 +3386,28 @@
         <v>16.61</v>
       </c>
       <c r="M24">
-        <v>1.952643</v>
+        <v>2.0413995</v>
       </c>
       <c r="N24">
-        <v>14.657357</v>
+        <v>14.5686005</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>14.657357</v>
+        <v>14.5686005</v>
       </c>
       <c r="Q24">
-        <v>16.347357</v>
+        <v>16.2586005</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1246776308454056</v>
+        <v>0.1257020156615797</v>
       </c>
       <c r="T24">
-        <v>0.6756487267068427</v>
+        <v>0.6844233854952433</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.506419248167738</v>
+        <v>8.13657493303001</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3432,22 +3432,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1090955520594163</v>
+        <v>0.1091725520594163</v>
       </c>
       <c r="C25">
-        <v>141.929738521797</v>
+        <v>140.1352574731756</v>
       </c>
       <c r="D25">
-        <v>174.976738521797</v>
+        <v>174.8412574731756</v>
       </c>
       <c r="E25">
-        <v>11.857</v>
+        <v>13.516</v>
       </c>
       <c r="F25">
-        <v>38.157</v>
+        <v>39.816</v>
       </c>
       <c r="G25">
         <v>5.11</v>
@@ -3468,28 +3468,28 @@
         <v>16.61</v>
       </c>
       <c r="M25">
-        <v>2.0413995</v>
+        <v>2.130156</v>
       </c>
       <c r="N25">
-        <v>14.5686005</v>
+        <v>14.479844</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>14.5686005</v>
+        <v>14.479844</v>
       </c>
       <c r="Q25">
-        <v>16.2586005</v>
+        <v>16.169844</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1257020156615797</v>
+        <v>0.1267533579729162</v>
       </c>
       <c r="T25">
-        <v>0.6844233854952433</v>
+        <v>0.6934289563570228</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.13657493303001</v>
+        <v>7.797550977487095</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3514,22 +3514,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1091725520594163</v>
+        <v>0.1094495520594164</v>
       </c>
       <c r="C26">
-        <v>140.1352574731756</v>
+        <v>137.990607693599</v>
       </c>
       <c r="D26">
-        <v>174.8412574731756</v>
+        <v>174.355607693599</v>
       </c>
       <c r="E26">
-        <v>13.516</v>
+        <v>15.175</v>
       </c>
       <c r="F26">
-        <v>39.816</v>
+        <v>41.475</v>
       </c>
       <c r="G26">
         <v>5.11</v>
@@ -3550,45 +3550,45 @@
         <v>16.61</v>
       </c>
       <c r="M26">
-        <v>2.130156</v>
+        <v>2.2520925</v>
       </c>
       <c r="N26">
-        <v>14.479844</v>
+        <v>14.3579075</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>14.479844</v>
+        <v>14.3579075</v>
       </c>
       <c r="Q26">
-        <v>16.169844</v>
+        <v>16.0479075</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1267533579729162</v>
+        <v>0.1278327360792218</v>
       </c>
       <c r="T26">
-        <v>0.6934289563570228</v>
+        <v>0.7026746757751164</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.797550977487095</v>
+        <v>7.37536313450713</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3596,22 +3596,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1094495520594164</v>
+        <v>0.1095345520594163</v>
       </c>
       <c r="C27">
-        <v>137.990607693599</v>
+        <v>136.1831220938231</v>
       </c>
       <c r="D27">
-        <v>174.355607693599</v>
+        <v>174.2071220938231</v>
       </c>
       <c r="E27">
-        <v>15.175</v>
+        <v>16.834</v>
       </c>
       <c r="F27">
-        <v>41.475</v>
+        <v>43.134</v>
       </c>
       <c r="G27">
         <v>5.11</v>
@@ -3632,28 +3632,28 @@
         <v>16.61</v>
       </c>
       <c r="M27">
-        <v>2.2520925</v>
+        <v>2.3421762</v>
       </c>
       <c r="N27">
-        <v>14.3579075</v>
+        <v>14.2678238</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>14.3579075</v>
+        <v>14.2678238</v>
       </c>
       <c r="Q27">
-        <v>16.0479075</v>
+        <v>15.9578238</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1278327360792218</v>
+        <v>0.1289412865667788</v>
       </c>
       <c r="T27">
-        <v>0.7026746757751164</v>
+        <v>0.7121702795018072</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.37536313450713</v>
+        <v>7.091695321641471</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3678,22 +3678,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1095345520594163</v>
+        <v>0.1096195520594163</v>
       </c>
       <c r="C28">
-        <v>136.1831220938231</v>
+        <v>134.3758891869545</v>
       </c>
       <c r="D28">
-        <v>174.2071220938231</v>
+        <v>174.0588891869545</v>
       </c>
       <c r="E28">
-        <v>16.834</v>
+        <v>18.49300000000001</v>
       </c>
       <c r="F28">
-        <v>43.134</v>
+        <v>44.79300000000001</v>
       </c>
       <c r="G28">
         <v>5.11</v>
@@ -3714,28 +3714,28 @@
         <v>16.61</v>
       </c>
       <c r="M28">
-        <v>2.3421762</v>
+        <v>2.4322599</v>
       </c>
       <c r="N28">
-        <v>14.2678238</v>
+        <v>14.1777401</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>14.2678238</v>
+        <v>14.1777401</v>
       </c>
       <c r="Q28">
-        <v>15.9578238</v>
+        <v>15.8677401</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1289412865667788</v>
+        <v>0.1300802083005703</v>
       </c>
       <c r="T28">
-        <v>0.7121702795018072</v>
+        <v>0.7219260367552567</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.091695321641471</v>
+        <v>6.829039939358453</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3760,22 +3760,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1096195520594163</v>
+        <v>0.1097045520594163</v>
       </c>
       <c r="C29">
-        <v>134.3758891869545</v>
+        <v>132.5689083284922</v>
       </c>
       <c r="D29">
-        <v>174.0588891869545</v>
+        <v>173.9109083284922</v>
       </c>
       <c r="E29">
-        <v>18.49300000000001</v>
+        <v>20.152</v>
       </c>
       <c r="F29">
-        <v>44.79300000000001</v>
+        <v>46.45200000000001</v>
       </c>
       <c r="G29">
         <v>5.11</v>
@@ -3796,28 +3796,28 @@
         <v>16.61</v>
       </c>
       <c r="M29">
-        <v>2.4322599</v>
+        <v>2.5223436</v>
       </c>
       <c r="N29">
-        <v>14.1777401</v>
+        <v>14.0876564</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>14.1777401</v>
+        <v>14.0876564</v>
       </c>
       <c r="Q29">
-        <v>15.8677401</v>
+        <v>15.7776564</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1300802083005703</v>
+        <v>0.1312507667491894</v>
       </c>
       <c r="T29">
-        <v>0.7219260367552567</v>
+        <v>0.7319527872657463</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.829039939358453</v>
+        <v>6.585145655809938</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3842,22 +3842,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1097045520594163</v>
+        <v>0.1097895520594164</v>
       </c>
       <c r="C30">
-        <v>132.5689083284922</v>
+        <v>130.7621788761251</v>
       </c>
       <c r="D30">
-        <v>173.9109083284922</v>
+        <v>173.7631788761251</v>
       </c>
       <c r="E30">
-        <v>20.152</v>
+        <v>21.811</v>
       </c>
       <c r="F30">
-        <v>46.45200000000001</v>
+        <v>48.111</v>
       </c>
       <c r="G30">
         <v>5.11</v>
@@ -3878,28 +3878,28 @@
         <v>16.61</v>
       </c>
       <c r="M30">
-        <v>2.5223436</v>
+        <v>2.6124273</v>
       </c>
       <c r="N30">
-        <v>14.0876564</v>
+        <v>13.9975727</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>14.0876564</v>
+        <v>13.9975727</v>
       </c>
       <c r="Q30">
-        <v>15.7776564</v>
+        <v>15.6875727</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1312507667491894</v>
+        <v>0.1324542986752343</v>
       </c>
       <c r="T30">
-        <v>0.7319527872657463</v>
+        <v>0.7422619814525879</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.585145655809938</v>
+        <v>6.35807166767856</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3924,22 +3924,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1097895520594163</v>
+        <v>0.1098745520594163</v>
       </c>
       <c r="C31">
-        <v>130.7621788761251</v>
+        <v>128.9557001897225</v>
       </c>
       <c r="D31">
-        <v>173.7631788761251</v>
+        <v>173.6157001897225</v>
       </c>
       <c r="E31">
-        <v>21.811</v>
+        <v>23.47</v>
       </c>
       <c r="F31">
-        <v>48.111</v>
+        <v>49.77</v>
       </c>
       <c r="G31">
         <v>5.11</v>
@@ -3960,28 +3960,28 @@
         <v>16.61</v>
       </c>
       <c r="M31">
-        <v>2.6124273</v>
+        <v>2.702511</v>
       </c>
       <c r="N31">
-        <v>13.9975727</v>
+        <v>13.907489</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>13.9975727</v>
+        <v>13.907489</v>
       </c>
       <c r="Q31">
-        <v>15.6875727</v>
+        <v>15.597489</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1324542986752343</v>
+        <v>0.1336922172277376</v>
       </c>
       <c r="T31">
-        <v>0.7422619814525878</v>
+        <v>0.7528657240447677</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.358071667678561</v>
+        <v>6.146135945422608</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1098745520594163</v>
+        <v>0.1102695520594163</v>
       </c>
       <c r="C32">
-        <v>128.9557001897225</v>
+        <v>126.6146298961827</v>
       </c>
       <c r="D32">
-        <v>173.6157001897225</v>
+        <v>172.9336298961827</v>
       </c>
       <c r="E32">
-        <v>23.47</v>
+        <v>25.129</v>
       </c>
       <c r="F32">
-        <v>49.77</v>
+        <v>51.429</v>
       </c>
       <c r="G32">
         <v>5.11</v>
@@ -4042,45 +4042,45 @@
         <v>16.61</v>
       </c>
       <c r="M32">
-        <v>2.702511</v>
+        <v>2.8440237</v>
       </c>
       <c r="N32">
-        <v>13.907489</v>
+        <v>13.7659763</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>13.907489</v>
+        <v>13.7659763</v>
       </c>
       <c r="Q32">
-        <v>15.597489</v>
+        <v>15.4559763</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1336922172277376</v>
+        <v>0.134966017477415</v>
       </c>
       <c r="T32">
-        <v>0.7528657240447677</v>
+        <v>0.7637768214946918</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0</v>
       </c>
       <c r="W32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.146135945422608</v>
+        <v>5.840317012829393</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4088,22 +4088,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1102695520594163</v>
+        <v>0.1103645520594164</v>
       </c>
       <c r="C33">
-        <v>126.6146298961827</v>
+        <v>124.7923863753969</v>
       </c>
       <c r="D33">
-        <v>172.9336298961827</v>
+        <v>172.7703863753968</v>
       </c>
       <c r="E33">
-        <v>25.129</v>
+        <v>26.788</v>
       </c>
       <c r="F33">
-        <v>51.429</v>
+        <v>53.088</v>
       </c>
       <c r="G33">
         <v>5.11</v>
@@ -4124,28 +4124,28 @@
         <v>16.61</v>
       </c>
       <c r="M33">
-        <v>2.8440237</v>
+        <v>2.9357664</v>
       </c>
       <c r="N33">
-        <v>13.7659763</v>
+        <v>13.6742336</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>13.7659763</v>
+        <v>13.6742336</v>
       </c>
       <c r="Q33">
-        <v>15.4559763</v>
+        <v>15.3642336</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.134966017477415</v>
+        <v>0.1362772824403182</v>
       </c>
       <c r="T33">
-        <v>0.7637768214946918</v>
+        <v>0.7750088335754962</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.840317012829393</v>
+        <v>5.657807106178474</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4170,22 +4170,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1103645520594164</v>
+        <v>0.1104595520594163</v>
       </c>
       <c r="C34">
-        <v>124.7923863753969</v>
+        <v>122.9704507567302</v>
       </c>
       <c r="D34">
-        <v>172.7703863753968</v>
+        <v>172.6074507567302</v>
       </c>
       <c r="E34">
-        <v>26.788</v>
+        <v>28.44700000000001</v>
       </c>
       <c r="F34">
-        <v>53.088</v>
+        <v>54.74700000000001</v>
       </c>
       <c r="G34">
         <v>5.11</v>
@@ -4206,28 +4206,28 @@
         <v>16.61</v>
       </c>
       <c r="M34">
-        <v>2.9357664</v>
+        <v>3.027509100000001</v>
       </c>
       <c r="N34">
-        <v>13.6742336</v>
+        <v>13.5824909</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>13.6742336</v>
+        <v>13.5824909</v>
       </c>
       <c r="Q34">
-        <v>15.3642336</v>
+        <v>15.2724909</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1362772824403182</v>
+        <v>0.1376276896409199</v>
       </c>
       <c r="T34">
-        <v>0.7750088335754962</v>
+        <v>0.786576129599011</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.657807106178474</v>
+        <v>5.486358405991248</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4252,22 +4252,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1104595520594163</v>
+        <v>0.1105545520594163</v>
       </c>
       <c r="C35">
-        <v>122.9704507567302</v>
+        <v>121.1488221698782</v>
       </c>
       <c r="D35">
-        <v>172.6074507567302</v>
+        <v>172.4448221698782</v>
       </c>
       <c r="E35">
-        <v>28.44700000000001</v>
+        <v>30.10600000000001</v>
       </c>
       <c r="F35">
-        <v>54.74700000000001</v>
+        <v>56.40600000000001</v>
       </c>
       <c r="G35">
         <v>5.11</v>
@@ -4288,28 +4288,28 @@
         <v>16.61</v>
       </c>
       <c r="M35">
-        <v>3.027509100000001</v>
+        <v>3.1192518</v>
       </c>
       <c r="N35">
-        <v>13.5824909</v>
+        <v>13.4907482</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>13.5824909</v>
+        <v>13.4907482</v>
       </c>
       <c r="Q35">
-        <v>15.2724909</v>
+        <v>15.1807482</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1376276896409199</v>
+        <v>0.139019018271843</v>
       </c>
       <c r="T35">
-        <v>0.786576129599011</v>
+        <v>0.7984939497444505</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.486358405991248</v>
+        <v>5.324994923462094</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4334,22 +4334,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1105545520594163</v>
+        <v>0.1106495520594163</v>
       </c>
       <c r="C36">
-        <v>121.1488221698782</v>
+        <v>119.3274997478131</v>
       </c>
       <c r="D36">
-        <v>172.4448221698782</v>
+        <v>172.2824997478131</v>
       </c>
       <c r="E36">
-        <v>30.10600000000001</v>
+        <v>31.765</v>
       </c>
       <c r="F36">
-        <v>56.40600000000001</v>
+        <v>58.065</v>
       </c>
       <c r="G36">
         <v>5.11</v>
@@ -4370,28 +4370,28 @@
         <v>16.61</v>
       </c>
       <c r="M36">
-        <v>3.1192518</v>
+        <v>3.2109945</v>
       </c>
       <c r="N36">
-        <v>13.4907482</v>
+        <v>13.3990055</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>13.4907482</v>
+        <v>13.3990055</v>
       </c>
       <c r="Q36">
-        <v>15.1807482</v>
+        <v>15.0890055</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.139019018271843</v>
+        <v>0.1404531570144867</v>
       </c>
       <c r="T36">
-        <v>0.7984939497444505</v>
+        <v>0.8107784720482114</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.324994923462094</v>
+        <v>5.172852211363177</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4416,22 +4416,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1106495520594163</v>
+        <v>0.1107445520594163</v>
       </c>
       <c r="C37">
-        <v>119.3274997478131</v>
+        <v>117.5064826267686</v>
       </c>
       <c r="D37">
-        <v>172.2824997478131</v>
+        <v>172.1204826267686</v>
       </c>
       <c r="E37">
-        <v>31.765</v>
+        <v>33.42400000000001</v>
       </c>
       <c r="F37">
-        <v>58.065</v>
+        <v>59.72400000000001</v>
       </c>
       <c r="G37">
         <v>5.11</v>
@@ -4452,28 +4452,28 @@
         <v>16.61</v>
       </c>
       <c r="M37">
-        <v>3.2109945</v>
+        <v>3.302737200000001</v>
       </c>
       <c r="N37">
-        <v>13.3990055</v>
+        <v>13.3072628</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>13.3990055</v>
+        <v>13.3072628</v>
       </c>
       <c r="Q37">
-        <v>15.0890055</v>
+        <v>14.9972628</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1404531570144867</v>
+        <v>0.141932112592838</v>
       </c>
       <c r="T37">
-        <v>0.8107784720482114</v>
+        <v>0.8234468856739646</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.172852211363177</v>
+        <v>5.029161872158643</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1107445520594163</v>
+        <v>0.1108395520594163</v>
       </c>
       <c r="C38">
-        <v>117.5064826267687</v>
+        <v>115.6857699462246</v>
       </c>
       <c r="D38">
-        <v>172.1204826267686</v>
+        <v>171.9587699462246</v>
       </c>
       <c r="E38">
-        <v>33.42399999999999</v>
+        <v>35.083</v>
       </c>
       <c r="F38">
-        <v>59.724</v>
+        <v>61.383</v>
       </c>
       <c r="G38">
         <v>5.11</v>
@@ -4534,28 +4534,28 @@
         <v>16.61</v>
       </c>
       <c r="M38">
-        <v>3.3027372</v>
+        <v>3.3944799</v>
       </c>
       <c r="N38">
-        <v>13.3072628</v>
+        <v>13.2155201</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>13.3072628</v>
+        <v>13.2155201</v>
       </c>
       <c r="Q38">
-        <v>14.9972628</v>
+        <v>14.9055201</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.141932112592838</v>
+        <v>0.1434580191419307</v>
       </c>
       <c r="T38">
-        <v>0.8234468856739646</v>
+        <v>0.8365174711608531</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.029161872158644</v>
+        <v>4.893238578316518</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1108395520594163</v>
+        <v>0.1109345520594164</v>
       </c>
       <c r="C39">
-        <v>115.6857699462246</v>
+        <v>113.8653608488919</v>
       </c>
       <c r="D39">
-        <v>171.9587699462246</v>
+        <v>171.7973608488919</v>
       </c>
       <c r="E39">
-        <v>35.083</v>
+        <v>36.742</v>
       </c>
       <c r="F39">
-        <v>61.383</v>
+        <v>63.042</v>
       </c>
       <c r="G39">
         <v>5.11</v>
@@ -4616,28 +4616,28 @@
         <v>16.61</v>
       </c>
       <c r="M39">
-        <v>3.3944799</v>
+        <v>3.4862226</v>
       </c>
       <c r="N39">
-        <v>13.2155201</v>
+        <v>13.1237774</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>13.2155201</v>
+        <v>13.1237774</v>
       </c>
       <c r="Q39">
-        <v>14.9055201</v>
+        <v>14.8137774</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1434580191419307</v>
+        <v>0.1450331484829296</v>
       </c>
       <c r="T39">
-        <v>0.8365174711608531</v>
+        <v>0.8500096884376408</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.893238578316518</v>
+        <v>4.764469142045032</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4662,22 +4662,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1109345520594164</v>
+        <v>0.1110295520594164</v>
       </c>
       <c r="C40">
-        <v>113.8653608488919</v>
+        <v>112.045254480697</v>
       </c>
       <c r="D40">
-        <v>171.7973608488919</v>
+        <v>171.636254480697</v>
       </c>
       <c r="E40">
-        <v>36.742</v>
+        <v>38.40100000000001</v>
       </c>
       <c r="F40">
-        <v>63.042</v>
+        <v>64.70100000000001</v>
       </c>
       <c r="G40">
         <v>5.11</v>
@@ -4698,28 +4698,28 @@
         <v>16.61</v>
       </c>
       <c r="M40">
-        <v>3.4862226</v>
+        <v>3.577965300000001</v>
       </c>
       <c r="N40">
-        <v>13.1237774</v>
+        <v>13.0320347</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>13.1237774</v>
+        <v>13.0320347</v>
       </c>
       <c r="Q40">
-        <v>14.8137774</v>
+        <v>14.7220347</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1450331484829296</v>
+        <v>0.1466599214088793</v>
       </c>
       <c r="T40">
-        <v>0.8500096884376408</v>
+        <v>0.8639442734939957</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.764469142045032</v>
+        <v>4.642303266607978</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1110295520594164</v>
+        <v>0.1111245520594163</v>
       </c>
       <c r="C41">
-        <v>112.045254480697</v>
+        <v>110.2254499907672</v>
       </c>
       <c r="D41">
-        <v>171.636254480697</v>
+        <v>171.4754499907672</v>
       </c>
       <c r="E41">
-        <v>38.40100000000001</v>
+        <v>40.06</v>
       </c>
       <c r="F41">
-        <v>64.70100000000001</v>
+        <v>66.36</v>
       </c>
       <c r="G41">
         <v>5.11</v>
@@ -4780,28 +4780,28 @@
         <v>16.61</v>
       </c>
       <c r="M41">
-        <v>3.577965300000001</v>
+        <v>3.669708</v>
       </c>
       <c r="N41">
-        <v>13.0320347</v>
+        <v>12.940292</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>13.0320347</v>
+        <v>12.940292</v>
       </c>
       <c r="Q41">
-        <v>14.7220347</v>
+        <v>14.630292</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1466599214088793</v>
+        <v>0.1483409200990272</v>
       </c>
       <c r="T41">
-        <v>0.8639442734939957</v>
+        <v>0.8783433447188956</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.642303266607978</v>
+        <v>4.52624568494278</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1111245520594163</v>
+        <v>0.1122445520594163</v>
       </c>
       <c r="C42">
-        <v>110.2254499907672</v>
+        <v>106.6931176525935</v>
       </c>
       <c r="D42">
-        <v>171.4754499907672</v>
+        <v>169.6021176525934</v>
       </c>
       <c r="E42">
-        <v>40.06</v>
+        <v>41.71900000000001</v>
       </c>
       <c r="F42">
-        <v>66.36</v>
+        <v>68.01900000000001</v>
       </c>
       <c r="G42">
         <v>5.11</v>
@@ -4862,45 +4862,45 @@
         <v>16.61</v>
       </c>
       <c r="M42">
-        <v>3.669708</v>
+        <v>3.9314982</v>
       </c>
       <c r="N42">
-        <v>12.940292</v>
+        <v>12.6785018</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>12.940292</v>
+        <v>12.6785018</v>
       </c>
       <c r="Q42">
-        <v>14.630292</v>
+        <v>14.3685018</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1483409200990272</v>
+        <v>0.1500789017956209</v>
       </c>
       <c r="T42">
-        <v>0.8783433447188956</v>
+        <v>0.8932305200531141</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0</v>
       </c>
       <c r="W42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.52624568494278</v>
+        <v>4.224852500250413</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4908,22 +4908,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1122445520594163</v>
+        <v>0.1123645520594163</v>
       </c>
       <c r="C43">
-        <v>106.6931176525935</v>
+        <v>104.8358283328082</v>
       </c>
       <c r="D43">
-        <v>169.6021176525934</v>
+        <v>169.4038283328082</v>
       </c>
       <c r="E43">
-        <v>41.71900000000001</v>
+        <v>43.37800000000001</v>
       </c>
       <c r="F43">
-        <v>68.01900000000001</v>
+        <v>69.67800000000001</v>
       </c>
       <c r="G43">
         <v>5.11</v>
@@ -4944,28 +4944,28 @@
         <v>16.61</v>
       </c>
       <c r="M43">
-        <v>3.9314982</v>
+        <v>4.027388400000001</v>
       </c>
       <c r="N43">
-        <v>12.6785018</v>
+        <v>12.5826116</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>12.6785018</v>
+        <v>12.5826116</v>
       </c>
       <c r="Q43">
-        <v>14.3685018</v>
+        <v>14.2726116</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1500789017956209</v>
+        <v>0.1518768138955454</v>
       </c>
       <c r="T43">
-        <v>0.8932305200531141</v>
+        <v>0.9086310462609265</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.224852500250413</v>
+        <v>4.124260774053973</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4990,22 +4990,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1123645520594164</v>
+        <v>0.1124845520594164</v>
       </c>
       <c r="C44">
-        <v>104.8358283328082</v>
+        <v>102.9790021291608</v>
       </c>
       <c r="D44">
-        <v>169.4038283328082</v>
+        <v>169.2060021291608</v>
       </c>
       <c r="E44">
-        <v>43.378</v>
+        <v>45.03700000000001</v>
       </c>
       <c r="F44">
-        <v>69.678</v>
+        <v>71.337</v>
       </c>
       <c r="G44">
         <v>5.11</v>
@@ -5026,28 +5026,28 @@
         <v>16.61</v>
       </c>
       <c r="M44">
-        <v>4.0273884</v>
+        <v>4.123278600000001</v>
       </c>
       <c r="N44">
-        <v>12.5826116</v>
+        <v>12.4867214</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>12.5826116</v>
+        <v>12.4867214</v>
       </c>
       <c r="Q44">
-        <v>14.2726116</v>
+        <v>14.1767214</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1518768138955454</v>
+        <v>0.153737810630555</v>
       </c>
       <c r="T44">
-        <v>0.9086310462609264</v>
+        <v>0.9245719418093638</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.124260774053974</v>
+        <v>4.028347732796905</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5072,22 +5072,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1124845520594164</v>
+        <v>0.1141445520594163</v>
       </c>
       <c r="C45">
-        <v>102.9790021291608</v>
+        <v>98.6300561740187</v>
       </c>
       <c r="D45">
-        <v>169.2060021291608</v>
+        <v>166.5160561740187</v>
       </c>
       <c r="E45">
-        <v>45.03700000000001</v>
+        <v>46.69600000000001</v>
       </c>
       <c r="F45">
-        <v>71.337</v>
+        <v>72.99600000000001</v>
       </c>
       <c r="G45">
         <v>5.11</v>
@@ -5108,45 +5108,45 @@
         <v>16.61</v>
       </c>
       <c r="M45">
-        <v>4.123278600000001</v>
+        <v>4.474654800000001</v>
       </c>
       <c r="N45">
-        <v>12.4867214</v>
+        <v>12.1353452</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>12.4867214</v>
+        <v>12.1353452</v>
       </c>
       <c r="Q45">
-        <v>14.1767214</v>
+        <v>13.8253452</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.153737810630555</v>
+        <v>0.155665271534672</v>
       </c>
       <c r="T45">
-        <v>0.9245719418093638</v>
+        <v>0.9410821550559595</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0</v>
       </c>
       <c r="W45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.028347732796905</v>
+        <v>3.712018187414144</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5154,22 +5154,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1141445520594163</v>
+        <v>0.1142995520594163</v>
       </c>
       <c r="C46">
-        <v>98.6300561740187</v>
+        <v>96.72424584716825</v>
       </c>
       <c r="D46">
-        <v>166.5160561740187</v>
+        <v>166.2692458471682</v>
       </c>
       <c r="E46">
-        <v>46.69600000000001</v>
+        <v>48.355</v>
       </c>
       <c r="F46">
-        <v>72.99600000000001</v>
+        <v>74.655</v>
       </c>
       <c r="G46">
         <v>5.11</v>
@@ -5190,28 +5190,28 @@
         <v>16.61</v>
       </c>
       <c r="M46">
-        <v>4.474654800000001</v>
+        <v>4.5763515</v>
       </c>
       <c r="N46">
-        <v>12.1353452</v>
+        <v>12.0336485</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>12.1353452</v>
+        <v>12.0336485</v>
       </c>
       <c r="Q46">
-        <v>13.8253452</v>
+        <v>13.7236485</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.155665271534672</v>
+        <v>0.1576628219262115</v>
       </c>
       <c r="T46">
-        <v>0.9410821550559595</v>
+        <v>0.9581927396933406</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.712018187414144</v>
+        <v>3.629528894360496</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5236,22 +5236,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1142995520594163</v>
+        <v>0.1144545520594164</v>
       </c>
       <c r="C47">
-        <v>96.72424584716825</v>
+        <v>94.8191660826872</v>
       </c>
       <c r="D47">
-        <v>166.2692458471682</v>
+        <v>166.0231660826872</v>
       </c>
       <c r="E47">
-        <v>48.355</v>
+        <v>50.01400000000001</v>
       </c>
       <c r="F47">
-        <v>74.655</v>
+        <v>76.31400000000001</v>
       </c>
       <c r="G47">
         <v>5.11</v>
@@ -5272,28 +5272,28 @@
         <v>16.61</v>
       </c>
       <c r="M47">
-        <v>4.5763515</v>
+        <v>4.6780482</v>
       </c>
       <c r="N47">
-        <v>12.0336485</v>
+        <v>11.9319518</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>12.0336485</v>
+        <v>11.9319518</v>
       </c>
       <c r="Q47">
-        <v>13.7236485</v>
+        <v>13.6219518</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1576628219262115</v>
+        <v>0.1597343556655858</v>
       </c>
       <c r="T47">
-        <v>0.9581927396933406</v>
+        <v>0.9759370496876618</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.629528894360496</v>
+        <v>3.550626092309181</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5318,22 +5318,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1144545520594164</v>
+        <v>0.1159255520594163</v>
       </c>
       <c r="C48">
-        <v>94.8191660826872</v>
+        <v>90.86054600210284</v>
       </c>
       <c r="D48">
-        <v>166.0231660826872</v>
+        <v>163.7235460021028</v>
       </c>
       <c r="E48">
-        <v>50.01400000000001</v>
+        <v>51.67300000000002</v>
       </c>
       <c r="F48">
-        <v>76.31400000000001</v>
+        <v>77.97300000000001</v>
       </c>
       <c r="G48">
         <v>5.11</v>
@@ -5354,45 +5354,45 @@
         <v>16.61</v>
       </c>
       <c r="M48">
-        <v>4.6780482</v>
+        <v>4.998069300000001</v>
       </c>
       <c r="N48">
-        <v>11.9319518</v>
+        <v>11.6119307</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>11.9319518</v>
+        <v>11.6119307</v>
       </c>
       <c r="Q48">
-        <v>13.6219518</v>
+        <v>13.3019307</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1597343556655858</v>
+        <v>0.1618840604894648</v>
       </c>
       <c r="T48">
-        <v>0.9759370496876618</v>
+        <v>0.9943509562855422</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0</v>
       </c>
       <c r="W48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.550626092309181</v>
+        <v>3.323283252595156</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5400,22 +5400,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1159255520594163</v>
+        <v>0.1161085520594164</v>
       </c>
       <c r="C49">
-        <v>90.86054600210284</v>
+        <v>88.91990930358057</v>
       </c>
       <c r="D49">
-        <v>163.7235460021028</v>
+        <v>163.4419093035806</v>
       </c>
       <c r="E49">
-        <v>51.67300000000002</v>
+        <v>53.33200000000001</v>
       </c>
       <c r="F49">
-        <v>77.97300000000001</v>
+        <v>79.63200000000001</v>
       </c>
       <c r="G49">
         <v>5.11</v>
@@ -5436,28 +5436,28 @@
         <v>16.61</v>
       </c>
       <c r="M49">
-        <v>4.998069300000001</v>
+        <v>5.1044112</v>
       </c>
       <c r="N49">
-        <v>11.6119307</v>
+        <v>11.5055888</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>11.6119307</v>
+        <v>11.5055888</v>
       </c>
       <c r="Q49">
-        <v>13.3019307</v>
+        <v>13.1955888</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1618840604894648</v>
+        <v>0.1641164462681084</v>
       </c>
       <c r="T49">
-        <v>0.9943509562855422</v>
+        <v>1.013473090060264</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.323283252595156</v>
+        <v>3.254048184832758</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5482,22 +5482,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1161085520594163</v>
+        <v>0.1162915520594164</v>
       </c>
       <c r="C50">
-        <v>88.9199093035806</v>
+        <v>86.98023988217298</v>
       </c>
       <c r="D50">
-        <v>163.4419093035806</v>
+        <v>163.161239882173</v>
       </c>
       <c r="E50">
-        <v>53.33200000000001</v>
+        <v>54.991</v>
       </c>
       <c r="F50">
-        <v>79.63200000000001</v>
+        <v>81.291</v>
       </c>
       <c r="G50">
         <v>5.11</v>
@@ -5518,28 +5518,28 @@
         <v>16.61</v>
       </c>
       <c r="M50">
-        <v>5.1044112</v>
+        <v>5.2107531</v>
       </c>
       <c r="N50">
-        <v>11.5055888</v>
+        <v>11.3992469</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>11.5055888</v>
+        <v>11.3992469</v>
       </c>
       <c r="Q50">
-        <v>13.1955888</v>
+        <v>13.0892469</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1641164462681083</v>
+        <v>0.1664363765870909</v>
       </c>
       <c r="T50">
-        <v>1.013473090060264</v>
+        <v>1.033345111433995</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.254048184832758</v>
+        <v>3.187639038203518</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5564,22 +5564,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1162915520594164</v>
+        <v>0.1164745520594163</v>
       </c>
       <c r="C51">
-        <v>86.98023988217298</v>
+        <v>85.04153276327402</v>
       </c>
       <c r="D51">
-        <v>163.161239882173</v>
+        <v>162.881532763274</v>
       </c>
       <c r="E51">
-        <v>54.991</v>
+        <v>56.65000000000001</v>
       </c>
       <c r="F51">
-        <v>81.291</v>
+        <v>82.95</v>
       </c>
       <c r="G51">
         <v>5.11</v>
@@ -5600,28 +5600,28 @@
         <v>16.61</v>
       </c>
       <c r="M51">
-        <v>5.2107531</v>
+        <v>5.317095</v>
       </c>
       <c r="N51">
-        <v>11.3992469</v>
+        <v>11.292905</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>11.3992469</v>
+        <v>11.292905</v>
       </c>
       <c r="Q51">
-        <v>13.0892469</v>
+        <v>12.982905</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1664363765870909</v>
+        <v>0.1688491041188327</v>
       </c>
       <c r="T51">
-        <v>1.033345111433995</v>
+        <v>1.054012013662675</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.187639038203518</v>
+        <v>3.123886257439448</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5646,22 +5646,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1164745520594163</v>
+        <v>0.1166575520594164</v>
       </c>
       <c r="C52">
-        <v>85.04153276327402</v>
+        <v>83.10378300633107</v>
       </c>
       <c r="D52">
-        <v>162.881532763274</v>
+        <v>162.6027830063311</v>
       </c>
       <c r="E52">
-        <v>56.65000000000001</v>
+        <v>58.30900000000001</v>
       </c>
       <c r="F52">
-        <v>82.95</v>
+        <v>84.60900000000001</v>
       </c>
       <c r="G52">
         <v>5.11</v>
@@ -5682,28 +5682,28 @@
         <v>16.61</v>
       </c>
       <c r="M52">
-        <v>5.317095</v>
+        <v>5.423436900000001</v>
       </c>
       <c r="N52">
-        <v>11.292905</v>
+        <v>11.1865631</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>11.292905</v>
+        <v>11.1865631</v>
       </c>
       <c r="Q52">
-        <v>12.982905</v>
+        <v>12.8765631</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1688491041188327</v>
+        <v>0.1713603103253395</v>
       </c>
       <c r="T52">
-        <v>1.054012013662675</v>
+        <v>1.075522462921097</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.123886257439448</v>
+        <v>3.062633585724948</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5728,22 +5728,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1166575520594164</v>
+        <v>0.1168405520594163</v>
       </c>
       <c r="C53">
-        <v>83.10378300633107</v>
+        <v>81.16698570455432</v>
       </c>
       <c r="D53">
-        <v>162.6027830063311</v>
+        <v>162.3249857045543</v>
       </c>
       <c r="E53">
-        <v>58.30900000000001</v>
+        <v>59.968</v>
       </c>
       <c r="F53">
-        <v>84.60900000000001</v>
+        <v>86.268</v>
       </c>
       <c r="G53">
         <v>5.11</v>
@@ -5764,28 +5764,28 @@
         <v>16.61</v>
       </c>
       <c r="M53">
-        <v>5.423436900000001</v>
+        <v>5.529778800000001</v>
       </c>
       <c r="N53">
-        <v>11.1865631</v>
+        <v>11.0802212</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>11.1865631</v>
+        <v>11.0802212</v>
       </c>
       <c r="Q53">
-        <v>12.8765631</v>
+        <v>12.7702212</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1713603103253395</v>
+        <v>0.1739761501237841</v>
       </c>
       <c r="T53">
-        <v>1.075522462921097</v>
+        <v>1.09792918089862</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.062633585724948</v>
+        <v>3.003736785999469</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5810,22 +5810,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1168405520594163</v>
+        <v>0.1211575520594163</v>
       </c>
       <c r="C54">
-        <v>81.16698570455432</v>
+        <v>73.21934508293769</v>
       </c>
       <c r="D54">
-        <v>162.3249857045543</v>
+        <v>156.0363450829377</v>
       </c>
       <c r="E54">
-        <v>59.968</v>
+        <v>61.62700000000001</v>
       </c>
       <c r="F54">
-        <v>86.268</v>
+        <v>87.92700000000001</v>
       </c>
       <c r="G54">
         <v>5.11</v>
@@ -5846,45 +5846,45 @@
         <v>16.61</v>
       </c>
       <c r="M54">
-        <v>5.529778800000001</v>
+        <v>6.321951300000001</v>
       </c>
       <c r="N54">
-        <v>11.0802212</v>
+        <v>10.2880487</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>11.0802212</v>
+        <v>10.2880487</v>
       </c>
       <c r="Q54">
-        <v>12.7702212</v>
+        <v>11.9780487</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1739761501237841</v>
+        <v>0.1767033022540773</v>
       </c>
       <c r="T54">
-        <v>1.09792918089862</v>
+        <v>1.121289376236888</v>
       </c>
       <c r="U54">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V54">
         <v>0</v>
       </c>
       <c r="W54">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.003736785999469</v>
+        <v>2.627353361611627</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5892,22 +5892,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1211575520594163</v>
+        <v>0.1214185520594163</v>
       </c>
       <c r="C55">
-        <v>73.21934508293769</v>
+        <v>71.19572582550953</v>
       </c>
       <c r="D55">
-        <v>156.0363450829377</v>
+        <v>155.6717258255095</v>
       </c>
       <c r="E55">
-        <v>61.62700000000001</v>
+        <v>63.28600000000002</v>
       </c>
       <c r="F55">
-        <v>87.92700000000001</v>
+        <v>89.58600000000001</v>
       </c>
       <c r="G55">
         <v>5.11</v>
@@ -5928,28 +5928,28 @@
         <v>16.61</v>
       </c>
       <c r="M55">
-        <v>6.321951300000001</v>
+        <v>6.441233400000002</v>
       </c>
       <c r="N55">
-        <v>10.2880487</v>
+        <v>10.1687666</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>10.2880487</v>
+        <v>10.1687666</v>
       </c>
       <c r="Q55">
-        <v>11.9780487</v>
+        <v>11.8587666</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1767033022540773</v>
+        <v>0.1795490262161225</v>
       </c>
       <c r="T55">
-        <v>1.121289376236888</v>
+        <v>1.145665232242038</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.627353361611627</v>
+        <v>2.57869866972993</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5974,22 +5974,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1214185520594163</v>
+        <v>0.1216795520594164</v>
       </c>
       <c r="C56">
-        <v>71.19572582550953</v>
+        <v>69.17380664970742</v>
       </c>
       <c r="D56">
-        <v>155.6717258255095</v>
+        <v>155.3088066497074</v>
       </c>
       <c r="E56">
-        <v>63.28600000000002</v>
+        <v>64.94500000000001</v>
       </c>
       <c r="F56">
-        <v>89.58600000000001</v>
+        <v>91.245</v>
       </c>
       <c r="G56">
         <v>5.11</v>
@@ -6010,28 +6010,28 @@
         <v>16.61</v>
       </c>
       <c r="M56">
-        <v>6.441233400000002</v>
+        <v>6.560515500000001</v>
       </c>
       <c r="N56">
-        <v>10.1687666</v>
+        <v>10.0494845</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>10.1687666</v>
+        <v>10.0494845</v>
       </c>
       <c r="Q56">
-        <v>11.8587666</v>
+        <v>11.7394845</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1795490262161225</v>
+        <v>0.182521226798703</v>
       </c>
       <c r="T56">
-        <v>1.145665232242038</v>
+        <v>1.171124459625194</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.57869866972993</v>
+        <v>2.531813239371204</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6056,22 +6056,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1216795520594164</v>
+        <v>0.1241245520594164</v>
       </c>
       <c r="C57">
-        <v>69.17380664970742</v>
+        <v>64.19546452991635</v>
       </c>
       <c r="D57">
-        <v>155.3088066497074</v>
+        <v>151.9894645299163</v>
       </c>
       <c r="E57">
-        <v>64.94500000000001</v>
+        <v>66.60400000000001</v>
       </c>
       <c r="F57">
-        <v>91.245</v>
+        <v>92.90400000000001</v>
       </c>
       <c r="G57">
         <v>5.11</v>
@@ -6092,45 +6092,45 @@
         <v>16.61</v>
       </c>
       <c r="M57">
-        <v>6.560515500000001</v>
+        <v>7.042123200000002</v>
       </c>
       <c r="N57">
-        <v>10.0494845</v>
+        <v>9.567876799999997</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>10.0494845</v>
+        <v>9.567876799999997</v>
       </c>
       <c r="Q57">
-        <v>11.7394845</v>
+        <v>11.2578768</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.182521226798703</v>
+        <v>0.1856285274077644</v>
       </c>
       <c r="T57">
-        <v>1.171124459625194</v>
+        <v>1.197740924616676</v>
       </c>
       <c r="U57">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0</v>
       </c>
       <c r="W57">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.531813239371204</v>
+        <v>2.358663648486012</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6138,22 +6138,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1241245520594164</v>
+        <v>0.1244245520594164</v>
       </c>
       <c r="C58">
-        <v>64.19546452991635</v>
+        <v>62.13893041076327</v>
       </c>
       <c r="D58">
-        <v>151.9894645299163</v>
+        <v>151.5919304107633</v>
       </c>
       <c r="E58">
-        <v>66.60400000000001</v>
+        <v>68.26300000000002</v>
       </c>
       <c r="F58">
-        <v>92.90400000000001</v>
+        <v>94.56300000000002</v>
       </c>
       <c r="G58">
         <v>5.11</v>
@@ -6174,28 +6174,28 @@
         <v>16.61</v>
       </c>
       <c r="M58">
-        <v>7.042123200000002</v>
+        <v>7.167875400000002</v>
       </c>
       <c r="N58">
-        <v>9.567876799999997</v>
+        <v>9.442124599999998</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>9.567876799999997</v>
+        <v>9.442124599999998</v>
       </c>
       <c r="Q58">
-        <v>11.2578768</v>
+        <v>11.1321246</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1856285274077644</v>
+        <v>0.1888803536265497</v>
       </c>
       <c r="T58">
-        <v>1.197740924616676</v>
+        <v>1.225595364724041</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.358663648486012</v>
+        <v>2.317283584477487</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6220,22 +6220,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1244245520594164</v>
+        <v>0.1247245520594163</v>
       </c>
       <c r="C59">
-        <v>62.13893041076327</v>
+        <v>60.08447039737109</v>
       </c>
       <c r="D59">
-        <v>151.5919304107633</v>
+        <v>151.1964703973711</v>
       </c>
       <c r="E59">
-        <v>68.26300000000002</v>
+        <v>69.92200000000001</v>
       </c>
       <c r="F59">
-        <v>94.56300000000002</v>
+        <v>96.22200000000001</v>
       </c>
       <c r="G59">
         <v>5.11</v>
@@ -6256,28 +6256,28 @@
         <v>16.61</v>
       </c>
       <c r="M59">
-        <v>7.167875400000002</v>
+        <v>7.293627600000002</v>
       </c>
       <c r="N59">
-        <v>9.442124599999998</v>
+        <v>9.316372399999999</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>9.442124599999998</v>
+        <v>9.316372399999999</v>
       </c>
       <c r="Q59">
-        <v>11.1321246</v>
+        <v>11.0063724</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1888803536265497</v>
+        <v>0.1922870287128961</v>
       </c>
       <c r="T59">
-        <v>1.225595364724041</v>
+        <v>1.25477620674128</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.317283584477487</v>
+        <v>2.277330419227875</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6302,22 +6302,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1247245520594163</v>
+        <v>0.1250245520594163</v>
       </c>
       <c r="C60">
-        <v>60.08447039737113</v>
+        <v>58.0320682997278</v>
       </c>
       <c r="D60">
-        <v>151.1964703973711</v>
+        <v>150.8030682997278</v>
       </c>
       <c r="E60">
-        <v>69.922</v>
+        <v>71.581</v>
       </c>
       <c r="F60">
-        <v>96.22199999999999</v>
+        <v>97.881</v>
       </c>
       <c r="G60">
         <v>5.11</v>
@@ -6338,28 +6338,28 @@
         <v>16.61</v>
       </c>
       <c r="M60">
-        <v>7.2936276</v>
+        <v>7.419379800000001</v>
       </c>
       <c r="N60">
-        <v>9.316372399999999</v>
+        <v>9.190620199999998</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>9.316372399999999</v>
+        <v>9.190620199999998</v>
       </c>
       <c r="Q60">
-        <v>11.0063724</v>
+        <v>10.8806202</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.192287028712896</v>
+        <v>0.1958598830717471</v>
       </c>
       <c r="T60">
-        <v>1.254776206741279</v>
+        <v>1.285380504466676</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.277330419227875</v>
+        <v>2.238731598562995</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6384,22 +6384,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1250245520594163</v>
+        <v>0.1253245520594164</v>
       </c>
       <c r="C61">
-        <v>58.0320682997278</v>
+        <v>55.98170809588491</v>
       </c>
       <c r="D61">
-        <v>150.8030682997278</v>
+        <v>150.4117080958849</v>
       </c>
       <c r="E61">
-        <v>71.581</v>
+        <v>73.24000000000001</v>
       </c>
       <c r="F61">
-        <v>97.881</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="G61">
         <v>5.11</v>
@@ -6420,28 +6420,28 @@
         <v>16.61</v>
       </c>
       <c r="M61">
-        <v>7.419379800000001</v>
+        <v>7.545132000000002</v>
       </c>
       <c r="N61">
-        <v>9.190620199999998</v>
+        <v>9.064867999999997</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>9.190620199999998</v>
+        <v>9.064867999999997</v>
       </c>
       <c r="Q61">
-        <v>10.8806202</v>
+        <v>10.754868</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1958598830717471</v>
+        <v>0.1996113801485409</v>
       </c>
       <c r="T61">
-        <v>1.285380504466676</v>
+        <v>1.317515017078343</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.238731598562995</v>
+        <v>2.201419405253612</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6466,22 +6466,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1253245520594164</v>
+        <v>0.1256245520594164</v>
       </c>
       <c r="C62">
-        <v>55.98170809588491</v>
+        <v>53.93337392978258</v>
       </c>
       <c r="D62">
-        <v>150.4117080958849</v>
+        <v>150.0223739297826</v>
       </c>
       <c r="E62">
-        <v>73.24000000000001</v>
+        <v>74.899</v>
       </c>
       <c r="F62">
-        <v>99.54000000000001</v>
+        <v>101.199</v>
       </c>
       <c r="G62">
         <v>5.11</v>
@@ -6502,28 +6502,28 @@
         <v>16.61</v>
       </c>
       <c r="M62">
-        <v>7.545132000000002</v>
+        <v>7.670884200000001</v>
       </c>
       <c r="N62">
-        <v>9.064867999999997</v>
+        <v>8.9391158</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>9.064867999999997</v>
+        <v>8.9391158</v>
       </c>
       <c r="Q62">
-        <v>10.754868</v>
+        <v>10.6291158</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1996113801485409</v>
+        <v>0.2035552616908111</v>
       </c>
       <c r="T62">
-        <v>1.317515017078343</v>
+        <v>1.351297453413685</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.201419405253612</v>
+        <v>2.165330562544537</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6548,22 +6548,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1256245520594164</v>
+        <v>0.1259245520594164</v>
       </c>
       <c r="C63">
-        <v>53.93337392978258</v>
+        <v>51.88705010910786</v>
       </c>
       <c r="D63">
-        <v>150.0223739297826</v>
+        <v>149.6350501091079</v>
       </c>
       <c r="E63">
-        <v>74.899</v>
+        <v>76.55800000000001</v>
       </c>
       <c r="F63">
-        <v>101.199</v>
+        <v>102.858</v>
       </c>
       <c r="G63">
         <v>5.11</v>
@@ -6584,28 +6584,28 @@
         <v>16.61</v>
       </c>
       <c r="M63">
-        <v>7.670884200000001</v>
+        <v>7.796636400000001</v>
       </c>
       <c r="N63">
-        <v>8.9391158</v>
+        <v>8.813363599999999</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>8.9391158</v>
+        <v>8.813363599999999</v>
       </c>
       <c r="Q63">
-        <v>10.6291158</v>
+        <v>10.5033636</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2035552616908111</v>
+        <v>0.2077067159458325</v>
       </c>
       <c r="T63">
-        <v>1.351297453413685</v>
+        <v>1.386857912714046</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.165330562544537</v>
+        <v>2.130405876051883</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6630,22 +6630,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1259245520594164</v>
+        <v>0.1262245520594164</v>
       </c>
       <c r="C64">
-        <v>51.88705010910786</v>
+        <v>49.84272110318652</v>
       </c>
       <c r="D64">
-        <v>149.6350501091079</v>
+        <v>149.2497211031865</v>
       </c>
       <c r="E64">
-        <v>76.55800000000001</v>
+        <v>78.21700000000001</v>
       </c>
       <c r="F64">
-        <v>102.858</v>
+        <v>104.517</v>
       </c>
       <c r="G64">
         <v>5.11</v>
@@ -6666,28 +6666,28 @@
         <v>16.61</v>
       </c>
       <c r="M64">
-        <v>7.796636400000001</v>
+        <v>7.922388600000001</v>
       </c>
       <c r="N64">
-        <v>8.813363599999999</v>
+        <v>8.687611399999998</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>8.813363599999999</v>
+        <v>8.687611399999998</v>
       </c>
       <c r="Q64">
-        <v>10.5033636</v>
+        <v>10.3776114</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2077067159458325</v>
+        <v>0.2120825731335577</v>
       </c>
       <c r="T64">
-        <v>1.386857912714046</v>
+        <v>1.424340559003614</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.130405876051883</v>
+        <v>2.096589909765345</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6712,22 +6712,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1262245520594164</v>
+        <v>0.1265245520594163</v>
       </c>
       <c r="C65">
-        <v>49.84272110318652</v>
+        <v>47.80037154090716</v>
       </c>
       <c r="D65">
-        <v>149.2497211031865</v>
+        <v>148.8663715409072</v>
       </c>
       <c r="E65">
-        <v>78.21700000000001</v>
+        <v>79.876</v>
       </c>
       <c r="F65">
-        <v>104.517</v>
+        <v>106.176</v>
       </c>
       <c r="G65">
         <v>5.11</v>
@@ -6748,28 +6748,28 @@
         <v>16.61</v>
       </c>
       <c r="M65">
-        <v>7.922388600000001</v>
+        <v>8.048140800000001</v>
       </c>
       <c r="N65">
-        <v>8.687611399999998</v>
+        <v>8.561859199999999</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>8.687611399999998</v>
+        <v>8.561859199999999</v>
       </c>
       <c r="Q65">
-        <v>10.3776114</v>
+        <v>10.2518592</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2120825731335577</v>
+        <v>0.2167015334983787</v>
       </c>
       <c r="T65">
-        <v>1.424340559003614</v>
+        <v>1.463905574531493</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.096589909765345</v>
+        <v>2.063830692425261</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6794,22 +6794,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1265245520594163</v>
+        <v>0.1268245520594164</v>
       </c>
       <c r="C66">
-        <v>47.80037154090716</v>
+        <v>45.75998620867725</v>
       </c>
       <c r="D66">
-        <v>148.8663715409072</v>
+        <v>148.4849862086772</v>
       </c>
       <c r="E66">
-        <v>79.876</v>
+        <v>81.53500000000001</v>
       </c>
       <c r="F66">
-        <v>106.176</v>
+        <v>107.835</v>
       </c>
       <c r="G66">
         <v>5.11</v>
@@ -6830,28 +6830,28 @@
         <v>16.61</v>
       </c>
       <c r="M66">
-        <v>8.048140800000001</v>
+        <v>8.173893000000001</v>
       </c>
       <c r="N66">
-        <v>8.561859199999999</v>
+        <v>8.436106999999998</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>8.561859199999999</v>
+        <v>8.436106999999998</v>
       </c>
       <c r="Q66">
-        <v>10.2518592</v>
+        <v>10.126107</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2167015334983787</v>
+        <v>0.2215844344554753</v>
       </c>
       <c r="T66">
-        <v>1.463905574531493</v>
+        <v>1.505731448089536</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.063830692425261</v>
+        <v>2.032079451003334</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6876,22 +6876,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1268245520594164</v>
+        <v>0.1271245520594164</v>
       </c>
       <c r="C67">
-        <v>45.75998620867725</v>
+        <v>43.72155004841066</v>
       </c>
       <c r="D67">
-        <v>148.4849862086772</v>
+        <v>148.1055500484107</v>
       </c>
       <c r="E67">
-        <v>81.53500000000001</v>
+        <v>83.19400000000002</v>
       </c>
       <c r="F67">
-        <v>107.835</v>
+        <v>109.494</v>
       </c>
       <c r="G67">
         <v>5.11</v>
@@ -6912,28 +6912,28 @@
         <v>16.61</v>
       </c>
       <c r="M67">
-        <v>8.173893000000001</v>
+        <v>8.299645200000002</v>
       </c>
       <c r="N67">
-        <v>8.436106999999998</v>
+        <v>8.310354799999997</v>
       </c>
       <c r="O67">
         <v>0</v>
       </c>
       <c r="P67">
-        <v>8.436106999999998</v>
+        <v>8.310354799999997</v>
       </c>
       <c r="Q67">
-        <v>10.126107</v>
+        <v>10.0003548</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2215844344554753</v>
+        <v>0.2267545648806363</v>
       </c>
       <c r="T67">
-        <v>1.505731448089536</v>
+        <v>1.550017667150992</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.032079451003334</v>
+        <v>2.001290368412374</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6958,22 +6958,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1271245520594164</v>
+        <v>0.1369385520594164</v>
       </c>
       <c r="C68">
-        <v>43.72155004841066</v>
+        <v>30.63678571781553</v>
       </c>
       <c r="D68">
-        <v>148.1055500484107</v>
+        <v>136.6797857178155</v>
       </c>
       <c r="E68">
-        <v>83.19400000000002</v>
+        <v>84.85300000000001</v>
       </c>
       <c r="F68">
-        <v>109.494</v>
+        <v>111.153</v>
       </c>
       <c r="G68">
         <v>5.11</v>
@@ -6994,45 +6994,45 @@
         <v>16.61</v>
       </c>
       <c r="M68">
-        <v>8.299645200000002</v>
+        <v>10.00377</v>
       </c>
       <c r="N68">
-        <v>8.310354799999997</v>
+        <v>6.60623</v>
       </c>
       <c r="O68">
         <v>0</v>
       </c>
       <c r="P68">
-        <v>8.310354799999997</v>
+        <v>6.60623</v>
       </c>
       <c r="Q68">
-        <v>10.0003548</v>
+        <v>8.29623</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2267545648806363</v>
+        <v>0.2322380365436859</v>
       </c>
       <c r="T68">
-        <v>1.550017667150992</v>
+        <v>1.596987899488901</v>
       </c>
       <c r="U68">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V68">
         <v>0</v>
       </c>
       <c r="W68">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.001290368412374</v>
+        <v>1.660374038987302</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7040,22 +7040,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1369385520594164</v>
+        <v>0.1373805520594163</v>
       </c>
       <c r="C69">
-        <v>30.63678571781553</v>
+        <v>28.50453846642307</v>
       </c>
       <c r="D69">
-        <v>136.6797857178155</v>
+        <v>136.2065384664231</v>
       </c>
       <c r="E69">
-        <v>84.85300000000001</v>
+        <v>86.51200000000001</v>
       </c>
       <c r="F69">
-        <v>111.153</v>
+        <v>112.812</v>
       </c>
       <c r="G69">
         <v>5.11</v>
@@ -7076,28 +7076,28 @@
         <v>16.61</v>
       </c>
       <c r="M69">
-        <v>10.00377</v>
+        <v>10.15308</v>
       </c>
       <c r="N69">
-        <v>6.60623</v>
+        <v>6.456919999999998</v>
       </c>
       <c r="O69">
         <v>0</v>
       </c>
       <c r="P69">
-        <v>6.60623</v>
+        <v>6.456919999999998</v>
       </c>
       <c r="Q69">
-        <v>8.29623</v>
+        <v>8.146919999999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2322380365436859</v>
+        <v>0.2380642251856761</v>
       </c>
       <c r="T69">
-        <v>1.596987899488901</v>
+        <v>1.646893771347929</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.660374038987302</v>
+        <v>1.635956773708076</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1373805520594163</v>
+        <v>0.1378225520594163</v>
       </c>
       <c r="C70">
-        <v>28.50453846642307</v>
+        <v>26.37555709922002</v>
       </c>
       <c r="D70">
-        <v>136.2065384664231</v>
+        <v>135.73655709922</v>
       </c>
       <c r="E70">
-        <v>86.51200000000001</v>
+        <v>88.17100000000002</v>
       </c>
       <c r="F70">
-        <v>112.812</v>
+        <v>114.471</v>
       </c>
       <c r="G70">
         <v>5.11</v>
@@ -7158,28 +7158,28 @@
         <v>16.61</v>
       </c>
       <c r="M70">
-        <v>10.15308</v>
+        <v>10.30239</v>
       </c>
       <c r="N70">
-        <v>6.456919999999998</v>
+        <v>6.307609999999999</v>
       </c>
       <c r="O70">
         <v>0</v>
       </c>
       <c r="P70">
-        <v>6.456919999999998</v>
+        <v>6.307609999999999</v>
       </c>
       <c r="Q70">
-        <v>8.146919999999998</v>
+        <v>7.997609999999998</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2380642251856761</v>
+        <v>0.2442662969658592</v>
       </c>
       <c r="T70">
-        <v>1.646893771347929</v>
+        <v>1.700019376875282</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.635956773708076</v>
+        <v>1.612247255248539</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7204,22 +7204,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1378225520594163</v>
+        <v>0.1382645520594163</v>
       </c>
       <c r="C71">
-        <v>26.37555709922002</v>
+        <v>24.249807925605</v>
       </c>
       <c r="D71">
-        <v>135.73655709922</v>
+        <v>135.269807925605</v>
       </c>
       <c r="E71">
-        <v>88.17100000000002</v>
+        <v>89.83000000000001</v>
       </c>
       <c r="F71">
-        <v>114.471</v>
+        <v>116.13</v>
       </c>
       <c r="G71">
         <v>5.11</v>
@@ -7240,28 +7240,28 @@
         <v>16.61</v>
       </c>
       <c r="M71">
-        <v>10.30239</v>
+        <v>10.4517</v>
       </c>
       <c r="N71">
-        <v>6.307609999999999</v>
+        <v>6.158299999999999</v>
       </c>
       <c r="O71">
         <v>0</v>
       </c>
       <c r="P71">
-        <v>6.307609999999999</v>
+        <v>6.158299999999999</v>
       </c>
       <c r="Q71">
-        <v>7.997609999999998</v>
+        <v>7.848299999999998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2442662969658592</v>
+        <v>0.2508818401980545</v>
       </c>
       <c r="T71">
-        <v>1.700019376875282</v>
+        <v>1.756686689437791</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.612247255248539</v>
+        <v>1.589215151602132</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7286,22 +7286,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1382645520594163</v>
+        <v>0.1387065520594163</v>
       </c>
       <c r="C72">
-        <v>24.249807925605</v>
+        <v>22.12725771678794</v>
       </c>
       <c r="D72">
-        <v>135.269807925605</v>
+        <v>134.8062577167879</v>
       </c>
       <c r="E72">
-        <v>89.83000000000001</v>
+        <v>91.48900000000002</v>
       </c>
       <c r="F72">
-        <v>116.13</v>
+        <v>117.789</v>
       </c>
       <c r="G72">
         <v>5.11</v>
@@ -7322,28 +7322,28 @@
         <v>16.61</v>
       </c>
       <c r="M72">
-        <v>10.4517</v>
+        <v>10.60101</v>
       </c>
       <c r="N72">
-        <v>6.158299999999999</v>
+        <v>6.008989999999999</v>
       </c>
       <c r="O72">
         <v>0</v>
       </c>
       <c r="P72">
-        <v>6.158299999999999</v>
+        <v>6.008989999999999</v>
       </c>
       <c r="Q72">
-        <v>7.848299999999998</v>
+        <v>7.698989999999998</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2508818401980545</v>
+        <v>0.2579536277910909</v>
       </c>
       <c r="T72">
-        <v>1.756686689437791</v>
+        <v>1.817262092521853</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.589215151602132</v>
+        <v>1.566831839607735</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7368,22 +7368,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1387065520594163</v>
+        <v>0.1391485520594163</v>
       </c>
       <c r="C73">
-        <v>22.12725771678795</v>
+        <v>20.00787369790463</v>
       </c>
       <c r="D73">
-        <v>134.8062577167879</v>
+        <v>134.3458736979046</v>
       </c>
       <c r="E73">
-        <v>91.489</v>
+        <v>93.148</v>
       </c>
       <c r="F73">
-        <v>117.789</v>
+        <v>119.448</v>
       </c>
       <c r="G73">
         <v>5.11</v>
@@ -7404,28 +7404,28 @@
         <v>16.61</v>
       </c>
       <c r="M73">
-        <v>10.60101</v>
+        <v>10.75032</v>
       </c>
       <c r="N73">
-        <v>6.008989999999999</v>
+        <v>5.859680000000001</v>
       </c>
       <c r="O73">
         <v>0</v>
       </c>
       <c r="P73">
-        <v>6.008989999999999</v>
+        <v>5.859680000000001</v>
       </c>
       <c r="Q73">
-        <v>7.698989999999998</v>
+        <v>7.54968</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2579536277910908</v>
+        <v>0.265530543069344</v>
       </c>
       <c r="T73">
-        <v>1.817262092521853</v>
+        <v>1.882164310111919</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.566831839607735</v>
+        <v>1.54507028627985</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7450,22 +7450,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1391485520594163</v>
+        <v>0.1395905520594163</v>
       </c>
       <c r="C74">
-        <v>20.00787369790463</v>
+        <v>17.89162354029148</v>
       </c>
       <c r="D74">
-        <v>134.3458736979046</v>
+        <v>133.8886235402915</v>
       </c>
       <c r="E74">
-        <v>93.148</v>
+        <v>94.807</v>
       </c>
       <c r="F74">
-        <v>119.448</v>
+        <v>121.107</v>
       </c>
       <c r="G74">
         <v>5.11</v>
@@ -7486,28 +7486,28 @@
         <v>16.61</v>
       </c>
       <c r="M74">
-        <v>10.75032</v>
+        <v>10.89963</v>
       </c>
       <c r="N74">
-        <v>5.859680000000001</v>
+        <v>5.710369999999999</v>
       </c>
       <c r="O74">
         <v>0</v>
       </c>
       <c r="P74">
-        <v>5.859680000000001</v>
+        <v>5.710369999999999</v>
       </c>
       <c r="Q74">
-        <v>7.54968</v>
+        <v>7.400369999999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.265530543069344</v>
+        <v>0.2736687113311716</v>
       </c>
       <c r="T74">
-        <v>1.882164310111919</v>
+        <v>1.951874099375323</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.54507028627985</v>
+        <v>1.523904939892455</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7532,22 +7532,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1395905520594163</v>
+        <v>0.1400325520594163</v>
       </c>
       <c r="C75">
-        <v>17.89162354029148</v>
+        <v>15.77847535391841</v>
       </c>
       <c r="D75">
-        <v>133.8886235402915</v>
+        <v>133.4344753539184</v>
       </c>
       <c r="E75">
-        <v>94.807</v>
+        <v>96.46600000000001</v>
       </c>
       <c r="F75">
-        <v>121.107</v>
+        <v>122.766</v>
       </c>
       <c r="G75">
         <v>5.11</v>
@@ -7568,28 +7568,28 @@
         <v>16.61</v>
       </c>
       <c r="M75">
-        <v>10.89963</v>
+        <v>11.04894</v>
       </c>
       <c r="N75">
-        <v>5.710369999999999</v>
+        <v>5.561059999999999</v>
       </c>
       <c r="O75">
         <v>0</v>
       </c>
       <c r="P75">
-        <v>5.710369999999999</v>
+        <v>5.561059999999999</v>
       </c>
       <c r="Q75">
-        <v>7.400369999999999</v>
+        <v>7.251059999999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2736687113311716</v>
+        <v>0.2824328925362167</v>
       </c>
       <c r="T75">
-        <v>1.951874099375323</v>
+        <v>2.026946180120528</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.523904939892455</v>
+        <v>1.503311629893908</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7614,22 +7614,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1400325520594163</v>
+        <v>0.1830745520594164</v>
       </c>
       <c r="C76">
-        <v>15.77847535391841</v>
+        <v>-19.01184105799514</v>
       </c>
       <c r="D76">
-        <v>133.4344753539184</v>
+        <v>100.3031589420049</v>
       </c>
       <c r="E76">
-        <v>96.46600000000001</v>
+        <v>98.12500000000001</v>
       </c>
       <c r="F76">
-        <v>122.766</v>
+        <v>124.425</v>
       </c>
       <c r="G76">
         <v>5.11</v>
@@ -7650,45 +7650,45 @@
         <v>16.61</v>
       </c>
       <c r="M76">
-        <v>11.04894</v>
+        <v>18.26559</v>
       </c>
       <c r="N76">
-        <v>5.561059999999999</v>
+        <v>-1.655590000000004</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P76">
-        <v>5.561059999999999</v>
+        <v>-1.655590000000004</v>
       </c>
       <c r="Q76">
-        <v>7.251059999999999</v>
+        <v>0.03440999999999628</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2824328925362167</v>
+        <v>0.2918982082376654</v>
       </c>
       <c r="T76">
-        <v>2.026946180120528</v>
+        <v>2.108024027325349</v>
       </c>
       <c r="U76">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V76">
         <v>0</v>
       </c>
       <c r="W76">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.503311629893908</v>
+        <v>0.9093601684916828</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7696,22 +7696,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1830745520594164</v>
+        <v>0.1840845520594164</v>
       </c>
       <c r="C77">
-        <v>-19.01184105799514</v>
+        <v>-21.25186115569328</v>
       </c>
       <c r="D77">
-        <v>100.3031589420049</v>
+        <v>99.72213884430673</v>
       </c>
       <c r="E77">
-        <v>98.12500000000001</v>
+        <v>99.78400000000001</v>
       </c>
       <c r="F77">
-        <v>124.425</v>
+        <v>126.084</v>
       </c>
       <c r="G77">
         <v>5.11</v>
@@ -7732,28 +7732,28 @@
         <v>16.61</v>
       </c>
       <c r="M77">
-        <v>18.26559</v>
+        <v>18.5091312</v>
       </c>
       <c r="N77">
-        <v>-1.655590000000004</v>
+        <v>-1.899131200000003</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-1.655590000000004</v>
+        <v>-1.899131200000003</v>
       </c>
       <c r="Q77">
-        <v>0.03440999999999628</v>
+        <v>-0.209131200000003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2918982082376654</v>
+        <v>0.3021523002475681</v>
       </c>
       <c r="T77">
-        <v>2.108024027325349</v>
+        <v>2.195858361797239</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9093601684916828</v>
+        <v>0.8973949031167923</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7778,22 +7778,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1840845520594164</v>
+        <v>0.1850945520594164</v>
       </c>
       <c r="C78">
-        <v>-21.25186115569328</v>
+        <v>-23.48518874011249</v>
       </c>
       <c r="D78">
-        <v>99.72213884430673</v>
+        <v>99.14781125988752</v>
       </c>
       <c r="E78">
-        <v>99.78400000000001</v>
+        <v>101.443</v>
       </c>
       <c r="F78">
-        <v>126.084</v>
+        <v>127.743</v>
       </c>
       <c r="G78">
         <v>5.11</v>
@@ -7814,28 +7814,28 @@
         <v>16.61</v>
       </c>
       <c r="M78">
-        <v>18.5091312</v>
+        <v>18.7526724</v>
       </c>
       <c r="N78">
-        <v>-1.899131200000003</v>
+        <v>-2.142672400000002</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-1.899131200000003</v>
+        <v>-2.142672400000002</v>
       </c>
       <c r="Q78">
-        <v>-0.209131200000003</v>
+        <v>-0.4526724000000022</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3021523002475681</v>
+        <v>0.313298052432245</v>
       </c>
       <c r="T78">
-        <v>2.195858361797239</v>
+        <v>2.291330464484076</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8973949031167923</v>
+        <v>0.8857404238555353</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7860,22 +7860,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1850945520594164</v>
+        <v>0.1861045520594163</v>
       </c>
       <c r="C79">
-        <v>-23.48518874011249</v>
+        <v>-25.71193878125484</v>
       </c>
       <c r="D79">
-        <v>99.14781125988752</v>
+        <v>98.58006121874517</v>
       </c>
       <c r="E79">
-        <v>101.443</v>
+        <v>103.102</v>
       </c>
       <c r="F79">
-        <v>127.743</v>
+        <v>129.402</v>
       </c>
       <c r="G79">
         <v>5.11</v>
@@ -7896,28 +7896,28 @@
         <v>16.61</v>
       </c>
       <c r="M79">
-        <v>18.7526724</v>
+        <v>18.9962136</v>
       </c>
       <c r="N79">
-        <v>-2.142672400000002</v>
+        <v>-2.386213600000005</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-2.142672400000002</v>
+        <v>-2.386213600000005</v>
       </c>
       <c r="Q79">
-        <v>-0.4526724000000022</v>
+        <v>-0.696213600000005</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.313298052432245</v>
+        <v>0.3254570548155289</v>
       </c>
       <c r="T79">
-        <v>2.291330464484076</v>
+        <v>2.395481849233352</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8857404238555353</v>
+        <v>0.8743847773958489</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7942,22 +7942,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1861045520594163</v>
+        <v>0.1871145520594164</v>
       </c>
       <c r="C80">
-        <v>-25.71193878125484</v>
+        <v>-27.93222363070572</v>
       </c>
       <c r="D80">
-        <v>98.58006121874517</v>
+        <v>98.01877636929429</v>
       </c>
       <c r="E80">
-        <v>103.102</v>
+        <v>104.761</v>
       </c>
       <c r="F80">
-        <v>129.402</v>
+        <v>131.061</v>
       </c>
       <c r="G80">
         <v>5.11</v>
@@ -7978,28 +7978,28 @@
         <v>16.61</v>
       </c>
       <c r="M80">
-        <v>18.9962136</v>
+        <v>19.2397548</v>
       </c>
       <c r="N80">
-        <v>-2.386213600000005</v>
+        <v>-2.629754800000004</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-2.386213600000005</v>
+        <v>-2.629754800000004</v>
       </c>
       <c r="Q80">
-        <v>-0.696213600000005</v>
+        <v>-0.9397548000000042</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3254570548155289</v>
+        <v>0.3387740574257921</v>
       </c>
       <c r="T80">
-        <v>2.395481849233352</v>
+        <v>2.509552413482559</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8743847773958489</v>
+        <v>0.8633166156566608</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8024,22 +8024,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1871145520594164</v>
+        <v>0.1881245520594164</v>
       </c>
       <c r="C81">
-        <v>-27.93222363070572</v>
+        <v>-30.14615309575407</v>
       </c>
       <c r="D81">
-        <v>98.01877636929429</v>
+        <v>97.46384690424593</v>
       </c>
       <c r="E81">
-        <v>104.761</v>
+        <v>106.42</v>
       </c>
       <c r="F81">
-        <v>131.061</v>
+        <v>132.72</v>
       </c>
       <c r="G81">
         <v>5.11</v>
@@ -8060,28 +8060,28 @@
         <v>16.61</v>
       </c>
       <c r="M81">
-        <v>19.2397548</v>
+        <v>19.483296</v>
       </c>
       <c r="N81">
-        <v>-2.629754800000004</v>
+        <v>-2.873296000000003</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-2.629754800000004</v>
+        <v>-2.873296000000003</v>
       </c>
       <c r="Q81">
-        <v>-0.9397548000000042</v>
+        <v>-1.183296000000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3387740574257921</v>
+        <v>0.3534227602970818</v>
       </c>
       <c r="T81">
-        <v>2.509552413482559</v>
+        <v>2.635030034156687</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8633166156566608</v>
+        <v>0.8525251579609526</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1881245520594164</v>
+        <v>0.1891345520594163</v>
       </c>
       <c r="C82">
-        <v>-30.14615309575407</v>
+        <v>-32.3538345110092</v>
       </c>
       <c r="D82">
-        <v>97.46384690424593</v>
+        <v>96.91516548899082</v>
       </c>
       <c r="E82">
-        <v>106.42</v>
+        <v>108.079</v>
       </c>
       <c r="F82">
-        <v>132.72</v>
+        <v>134.379</v>
       </c>
       <c r="G82">
         <v>5.11</v>
@@ -8142,28 +8142,28 @@
         <v>16.61</v>
       </c>
       <c r="M82">
-        <v>19.483296</v>
+        <v>19.72683720000001</v>
       </c>
       <c r="N82">
-        <v>-2.873296000000003</v>
+        <v>-3.116837200000006</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-2.873296000000003</v>
+        <v>-3.116837200000006</v>
       </c>
       <c r="Q82">
-        <v>-1.183296000000003</v>
+        <v>-1.426837200000006</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3534227602970818</v>
+        <v>0.369613431891665</v>
       </c>
       <c r="T82">
-        <v>2.635030034156687</v>
+        <v>2.773715825428092</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8525251579609526</v>
+        <v>0.8420001560108173</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8188,22 +8188,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1891345520594163</v>
+        <v>0.1901445520594164</v>
       </c>
       <c r="C83">
-        <v>-32.3538345110092</v>
+        <v>-34.55537280761189</v>
       </c>
       <c r="D83">
-        <v>96.91516548899082</v>
+        <v>96.37262719238812</v>
       </c>
       <c r="E83">
-        <v>108.079</v>
+        <v>109.738</v>
       </c>
       <c r="F83">
-        <v>134.379</v>
+        <v>136.038</v>
       </c>
       <c r="G83">
         <v>5.11</v>
@@ -8224,28 +8224,28 @@
         <v>16.61</v>
       </c>
       <c r="M83">
-        <v>19.72683720000001</v>
+        <v>19.9703784</v>
       </c>
       <c r="N83">
-        <v>-3.116837200000006</v>
+        <v>-3.360378400000005</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-3.116837200000006</v>
+        <v>-3.360378400000005</v>
       </c>
       <c r="Q83">
-        <v>-1.426837200000006</v>
+        <v>-1.670378400000005</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.369613431891665</v>
+        <v>0.3876030669967576</v>
       </c>
       <c r="T83">
-        <v>2.773715825428092</v>
+        <v>2.927811149062986</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8420001560108173</v>
+        <v>0.8317318614253195</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8270,22 +8270,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1901445520594164</v>
+        <v>0.1911545520594164</v>
       </c>
       <c r="C84">
-        <v>-34.55537280761189</v>
+        <v>-36.75087058013392</v>
       </c>
       <c r="D84">
-        <v>96.37262719238812</v>
+        <v>95.83612941986608</v>
       </c>
       <c r="E84">
-        <v>109.738</v>
+        <v>111.397</v>
       </c>
       <c r="F84">
-        <v>136.038</v>
+        <v>137.697</v>
       </c>
       <c r="G84">
         <v>5.11</v>
@@ -8306,28 +8306,28 @@
         <v>16.61</v>
       </c>
       <c r="M84">
-        <v>19.9703784</v>
+        <v>20.2139196</v>
       </c>
       <c r="N84">
-        <v>-3.360378400000005</v>
+        <v>-3.603919600000001</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-3.360378400000005</v>
+        <v>-3.603919600000001</v>
       </c>
       <c r="Q84">
-        <v>-1.670378400000005</v>
+        <v>-1.913919600000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3876030669967576</v>
+        <v>0.4077091297612728</v>
       </c>
       <c r="T84">
-        <v>2.927811149062986</v>
+        <v>3.100035334301986</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8317318614253195</v>
+        <v>0.8217109956250147</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8352,22 +8352,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1911545520594164</v>
+        <v>0.1921645520594163</v>
       </c>
       <c r="C85">
-        <v>-36.75087058013392</v>
+        <v>-38.9404281512554</v>
       </c>
       <c r="D85">
-        <v>95.83612941986608</v>
+        <v>95.30557184874462</v>
       </c>
       <c r="E85">
-        <v>111.397</v>
+        <v>113.056</v>
       </c>
       <c r="F85">
-        <v>137.697</v>
+        <v>139.356</v>
       </c>
       <c r="G85">
         <v>5.11</v>
@@ -8388,28 +8388,28 @@
         <v>16.61</v>
       </c>
       <c r="M85">
-        <v>20.2139196</v>
+        <v>20.45746080000001</v>
       </c>
       <c r="N85">
-        <v>-3.603919600000001</v>
+        <v>-3.847460800000007</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-3.603919600000001</v>
+        <v>-3.847460800000007</v>
       </c>
       <c r="Q85">
-        <v>-1.913919600000001</v>
+        <v>-2.157460800000008</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4077091297612728</v>
+        <v>0.4303284503713524</v>
       </c>
       <c r="T85">
-        <v>3.100035334301986</v>
+        <v>3.29378754269586</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8217109956250147</v>
+        <v>0.8119287218675738</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8434,22 +8434,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1921645520594163</v>
+        <v>0.1931745520594164</v>
       </c>
       <c r="C86">
-        <v>-38.94042815125538</v>
+        <v>-41.1241436343055</v>
       </c>
       <c r="D86">
-        <v>95.30557184874462</v>
+        <v>94.78085636569452</v>
       </c>
       <c r="E86">
-        <v>113.056</v>
+        <v>114.715</v>
       </c>
       <c r="F86">
-        <v>139.356</v>
+        <v>141.015</v>
       </c>
       <c r="G86">
         <v>5.11</v>
@@ -8470,28 +8470,28 @@
         <v>16.61</v>
       </c>
       <c r="M86">
-        <v>20.4574608</v>
+        <v>20.701002</v>
       </c>
       <c r="N86">
-        <v>-3.8474608</v>
+        <v>-4.091002000000003</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-3.8474608</v>
+        <v>-4.091002000000003</v>
       </c>
       <c r="Q86">
-        <v>-2.1574608</v>
+        <v>-2.401002000000003</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4303284503713521</v>
+        <v>0.455963680396109</v>
       </c>
       <c r="T86">
-        <v>3.293787542695858</v>
+        <v>3.513373378875582</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8119287218675741</v>
+        <v>0.8023766192573673</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8516,22 +8516,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1931745520594164</v>
+        <v>0.2406245520594164</v>
       </c>
       <c r="C87">
-        <v>-41.1241436343055</v>
+        <v>-62.2606989159013</v>
       </c>
       <c r="D87">
-        <v>94.78085636569452</v>
+        <v>75.30330108409871</v>
       </c>
       <c r="E87">
-        <v>114.715</v>
+        <v>116.374</v>
       </c>
       <c r="F87">
-        <v>141.015</v>
+        <v>142.674</v>
       </c>
       <c r="G87">
         <v>5.11</v>
@@ -8552,45 +8552,45 @@
         <v>16.61</v>
       </c>
       <c r="M87">
-        <v>20.701002</v>
+        <v>28.6489392</v>
       </c>
       <c r="N87">
-        <v>-4.091002000000003</v>
+        <v>-12.0389392</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-4.091002000000003</v>
+        <v>-12.0389392</v>
       </c>
       <c r="Q87">
-        <v>-2.401002000000003</v>
+        <v>-10.3489392</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.455963680396109</v>
+        <v>0.4852610861386881</v>
       </c>
       <c r="T87">
-        <v>3.513373378875582</v>
+        <v>3.764328620223838</v>
       </c>
       <c r="U87">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
         <v>0</v>
       </c>
       <c r="W87">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.8023766192573673</v>
+        <v>0.5797771388338175</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8598,22 +8598,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2406245520594164</v>
+        <v>0.2421745520594163</v>
       </c>
       <c r="C88">
-        <v>-62.2606989159013</v>
+        <v>-64.42183066925146</v>
       </c>
       <c r="D88">
-        <v>75.30330108409871</v>
+        <v>74.80116933074854</v>
       </c>
       <c r="E88">
-        <v>116.374</v>
+        <v>118.033</v>
       </c>
       <c r="F88">
-        <v>142.674</v>
+        <v>144.333</v>
       </c>
       <c r="G88">
         <v>5.11</v>
@@ -8634,28 +8634,28 @@
         <v>16.61</v>
       </c>
       <c r="M88">
-        <v>28.6489392</v>
+        <v>28.9820664</v>
       </c>
       <c r="N88">
-        <v>-12.0389392</v>
+        <v>-12.3720664</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-12.0389392</v>
+        <v>-12.3720664</v>
       </c>
       <c r="Q88">
-        <v>-10.3489392</v>
+        <v>-10.6820664</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4852610861386881</v>
+        <v>0.5190657850724333</v>
       </c>
       <c r="T88">
-        <v>3.764328620223838</v>
+        <v>4.053892360241056</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5797771388338175</v>
+        <v>0.5731130337897508</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8680,22 +8680,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2421745520594163</v>
+        <v>0.2437245520594163</v>
       </c>
       <c r="C89">
-        <v>-64.42183066925146</v>
+        <v>-66.57631022662346</v>
       </c>
       <c r="D89">
-        <v>74.80116933074854</v>
+        <v>74.30568977337656</v>
       </c>
       <c r="E89">
-        <v>118.033</v>
+        <v>119.692</v>
       </c>
       <c r="F89">
-        <v>144.333</v>
+        <v>145.992</v>
       </c>
       <c r="G89">
         <v>5.11</v>
@@ -8716,28 +8716,28 @@
         <v>16.61</v>
       </c>
       <c r="M89">
-        <v>28.9820664</v>
+        <v>29.3151936</v>
       </c>
       <c r="N89">
-        <v>-12.3720664</v>
+        <v>-12.7051936</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-12.3720664</v>
+        <v>-12.7051936</v>
       </c>
       <c r="Q89">
-        <v>-10.6820664</v>
+        <v>-11.01519360000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5190657850724333</v>
+        <v>0.5585046004951362</v>
       </c>
       <c r="T89">
-        <v>4.053892360241056</v>
+        <v>4.391716723594478</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5731130337897508</v>
+        <v>0.5666003856785035</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8762,22 +8762,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2437245520594163</v>
+        <v>0.2452745520594163</v>
       </c>
       <c r="C90">
-        <v>-66.57631022662346</v>
+        <v>-68.72426890968299</v>
       </c>
       <c r="D90">
-        <v>74.30568977337656</v>
+        <v>73.81673109031702</v>
       </c>
       <c r="E90">
-        <v>119.692</v>
+        <v>121.351</v>
       </c>
       <c r="F90">
-        <v>145.992</v>
+        <v>147.651</v>
       </c>
       <c r="G90">
         <v>5.11</v>
@@ -8798,28 +8798,28 @@
         <v>16.61</v>
       </c>
       <c r="M90">
-        <v>29.3151936</v>
+        <v>29.6483208</v>
       </c>
       <c r="N90">
-        <v>-12.7051936</v>
+        <v>-13.0383208</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-12.7051936</v>
+        <v>-13.0383208</v>
       </c>
       <c r="Q90">
-        <v>-11.01519360000001</v>
+        <v>-11.34832080000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5585046004951362</v>
+        <v>0.6051141096310577</v>
       </c>
       <c r="T90">
-        <v>4.391716723594478</v>
+        <v>4.790963698466704</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5666003856785035</v>
+        <v>0.5602340892102057</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2452745520594163</v>
+        <v>0.2468245520594164</v>
       </c>
       <c r="C91">
-        <v>-68.72426890968299</v>
+        <v>-70.86583460611385</v>
       </c>
       <c r="D91">
-        <v>73.81673109031702</v>
+        <v>73.33416539388615</v>
       </c>
       <c r="E91">
-        <v>121.351</v>
+        <v>123.01</v>
       </c>
       <c r="F91">
-        <v>147.651</v>
+        <v>149.31</v>
       </c>
       <c r="G91">
         <v>5.11</v>
@@ -8880,28 +8880,28 @@
         <v>16.61</v>
       </c>
       <c r="M91">
-        <v>29.6483208</v>
+        <v>29.981448</v>
       </c>
       <c r="N91">
-        <v>-13.0383208</v>
+        <v>-13.371448</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-13.0383208</v>
+        <v>-13.371448</v>
       </c>
       <c r="Q91">
-        <v>-11.34832080000001</v>
+        <v>-11.681448</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6051141096310577</v>
+        <v>0.6610455205941635</v>
       </c>
       <c r="T91">
-        <v>4.790963698466704</v>
+        <v>5.270060068313374</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5602340892102057</v>
+        <v>0.554009265996759</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8926,22 +8926,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2468245520594164</v>
+        <v>0.2483745520594163</v>
       </c>
       <c r="C92">
-        <v>-70.86583460611385</v>
+        <v>-73.0011318811345</v>
       </c>
       <c r="D92">
-        <v>73.33416539388615</v>
+        <v>72.85786811886553</v>
       </c>
       <c r="E92">
-        <v>123.01</v>
+        <v>124.669</v>
       </c>
       <c r="F92">
-        <v>149.31</v>
+        <v>150.969</v>
       </c>
       <c r="G92">
         <v>5.11</v>
@@ -8962,28 +8962,28 @@
         <v>16.61</v>
       </c>
       <c r="M92">
-        <v>29.981448</v>
+        <v>30.3145752</v>
       </c>
       <c r="N92">
-        <v>-13.371448</v>
+        <v>-13.7045752</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-13.371448</v>
+        <v>-13.7045752</v>
       </c>
       <c r="Q92">
-        <v>-11.681448</v>
+        <v>-12.0145752</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6610455205941635</v>
+        <v>0.7294061339935151</v>
       </c>
       <c r="T92">
-        <v>5.270060068313374</v>
+        <v>5.855622298125972</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.554009265996759</v>
+        <v>0.5479212520847067</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9008,22 +9008,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2483745520594163</v>
+        <v>0.2499245520594164</v>
       </c>
       <c r="C93">
-        <v>-73.0011318811345</v>
+        <v>-75.13028208469699</v>
       </c>
       <c r="D93">
-        <v>72.85786811886553</v>
+        <v>72.38771791530303</v>
       </c>
       <c r="E93">
-        <v>124.669</v>
+        <v>126.328</v>
       </c>
       <c r="F93">
-        <v>150.969</v>
+        <v>152.628</v>
       </c>
       <c r="G93">
         <v>5.11</v>
@@ -9044,28 +9044,28 @@
         <v>16.61</v>
       </c>
       <c r="M93">
-        <v>30.3145752</v>
+        <v>30.6477024</v>
       </c>
       <c r="N93">
-        <v>-13.7045752</v>
+        <v>-14.0377024</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-13.7045752</v>
+        <v>-14.0377024</v>
       </c>
       <c r="Q93">
-        <v>-12.0145752</v>
+        <v>-12.3477024</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7294061339935151</v>
+        <v>0.8148569007427047</v>
       </c>
       <c r="T93">
-        <v>5.855622298125972</v>
+        <v>6.587575085391721</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5479212520847067</v>
+        <v>0.5419655863011772</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9090,22 +9090,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2499245520594164</v>
+        <v>0.2514745520594164</v>
       </c>
       <c r="C94">
-        <v>-75.13028208469699</v>
+        <v>-77.25340345456215</v>
       </c>
       <c r="D94">
-        <v>72.38771791530303</v>
+        <v>71.92359654543786</v>
       </c>
       <c r="E94">
-        <v>126.328</v>
+        <v>127.987</v>
       </c>
       <c r="F94">
-        <v>152.628</v>
+        <v>154.287</v>
       </c>
       <c r="G94">
         <v>5.11</v>
@@ -9126,28 +9126,28 @@
         <v>16.61</v>
       </c>
       <c r="M94">
-        <v>30.6477024</v>
+        <v>30.9808296</v>
       </c>
       <c r="N94">
-        <v>-14.0377024</v>
+        <v>-14.3708296</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-14.0377024</v>
+        <v>-14.3708296</v>
       </c>
       <c r="Q94">
-        <v>-12.3477024</v>
+        <v>-12.6808296</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8148569007427047</v>
+        <v>0.9247221722773769</v>
       </c>
       <c r="T94">
-        <v>6.587575085391721</v>
+        <v>7.528657240447681</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5419655863011772</v>
+        <v>0.5361379993517023</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9172,22 +9172,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2514745520594164</v>
+        <v>0.2530245520594164</v>
       </c>
       <c r="C95">
-        <v>-77.25340345456215</v>
+        <v>-79.37061121543465</v>
       </c>
       <c r="D95">
-        <v>71.92359654543786</v>
+        <v>71.46538878456538</v>
       </c>
       <c r="E95">
-        <v>127.987</v>
+        <v>129.646</v>
       </c>
       <c r="F95">
-        <v>154.287</v>
+        <v>155.946</v>
       </c>
       <c r="G95">
         <v>5.11</v>
@@ -9208,28 +9208,28 @@
         <v>16.61</v>
       </c>
       <c r="M95">
-        <v>30.9808296</v>
+        <v>31.31395680000001</v>
       </c>
       <c r="N95">
-        <v>-14.3708296</v>
+        <v>-14.70395680000001</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-14.3708296</v>
+        <v>-14.70395680000001</v>
       </c>
       <c r="Q95">
-        <v>-12.6808296</v>
+        <v>-13.01395680000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9247221722773769</v>
+        <v>1.071209200990273</v>
       </c>
       <c r="T95">
-        <v>7.528657240447681</v>
+        <v>8.783433447188964</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5361379993517023</v>
+        <v>0.5304344036139181</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9254,22 +9254,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2530245520594164</v>
+        <v>0.2545745520594164</v>
       </c>
       <c r="C96">
-        <v>-79.37061121543465</v>
+        <v>-81.48201767433252</v>
       </c>
       <c r="D96">
-        <v>71.46538878456538</v>
+        <v>71.01298232566749</v>
       </c>
       <c r="E96">
-        <v>129.646</v>
+        <v>131.305</v>
       </c>
       <c r="F96">
-        <v>155.946</v>
+        <v>157.605</v>
       </c>
       <c r="G96">
         <v>5.11</v>
@@ -9290,28 +9290,28 @@
         <v>16.61</v>
       </c>
       <c r="M96">
-        <v>31.31395680000001</v>
+        <v>31.647084</v>
       </c>
       <c r="N96">
-        <v>-14.70395680000001</v>
+        <v>-15.037084</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-14.70395680000001</v>
+        <v>-15.037084</v>
       </c>
       <c r="Q96">
-        <v>-13.01395680000001</v>
+        <v>-13.347084</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.071209200990273</v>
+        <v>1.276291041188329</v>
       </c>
       <c r="T96">
-        <v>8.783433447188964</v>
+        <v>10.54012013662676</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5304344036139181</v>
+        <v>0.5248508835758769</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9336,22 +9336,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2545745520594164</v>
+        <v>0.2561245520594164</v>
       </c>
       <c r="C97">
-        <v>-81.48201767433252</v>
+        <v>-83.5877323123574</v>
       </c>
       <c r="D97">
-        <v>71.01298232566749</v>
+        <v>70.56626768764261</v>
       </c>
       <c r="E97">
-        <v>131.305</v>
+        <v>132.964</v>
       </c>
       <c r="F97">
-        <v>157.605</v>
+        <v>159.264</v>
       </c>
       <c r="G97">
         <v>5.11</v>
@@ -9372,28 +9372,28 @@
         <v>16.61</v>
       </c>
       <c r="M97">
-        <v>31.647084</v>
+        <v>31.9802112</v>
       </c>
       <c r="N97">
-        <v>-15.037084</v>
+        <v>-15.3702112</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-15.037084</v>
+        <v>-15.3702112</v>
       </c>
       <c r="Q97">
-        <v>-13.347084</v>
+        <v>-13.6802112</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.276291041188329</v>
+        <v>1.583913801485411</v>
       </c>
       <c r="T97">
-        <v>10.54012013662676</v>
+        <v>13.17515017078346</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5248508835758769</v>
+        <v>0.5193836868719616</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9418,22 +9418,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2561245520594164</v>
+        <v>0.2576745520594164</v>
       </c>
       <c r="C98">
-        <v>-83.5877323123574</v>
+        <v>-85.68786187302248</v>
       </c>
       <c r="D98">
-        <v>70.56626768764261</v>
+        <v>70.12513812697752</v>
       </c>
       <c r="E98">
-        <v>132.964</v>
+        <v>134.623</v>
       </c>
       <c r="F98">
-        <v>159.264</v>
+        <v>160.923</v>
       </c>
       <c r="G98">
         <v>5.11</v>
@@ -9454,28 +9454,28 @@
         <v>16.61</v>
       </c>
       <c r="M98">
-        <v>31.9802112</v>
+        <v>32.3133384</v>
       </c>
       <c r="N98">
-        <v>-15.3702112</v>
+        <v>-15.7033384</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-15.3702112</v>
+        <v>-15.7033384</v>
       </c>
       <c r="Q98">
-        <v>-13.6802112</v>
+        <v>-14.0133384</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.583913801485408</v>
+        <v>2.096618401980543</v>
       </c>
       <c r="T98">
-        <v>13.17515017078342</v>
+        <v>17.5668668943779</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5193836868719616</v>
+        <v>0.5140292158732815</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9500,22 +9500,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2576745520594164</v>
+        <v>0.2592245520594164</v>
       </c>
       <c r="C99">
-        <v>-85.68786187302248</v>
+        <v>-87.78251044728802</v>
       </c>
       <c r="D99">
-        <v>70.12513812697752</v>
+        <v>69.68948955271198</v>
       </c>
       <c r="E99">
-        <v>134.623</v>
+        <v>136.282</v>
       </c>
       <c r="F99">
-        <v>160.923</v>
+        <v>162.582</v>
       </c>
       <c r="G99">
         <v>5.11</v>
@@ -9536,28 +9536,28 @@
         <v>16.61</v>
       </c>
       <c r="M99">
-        <v>32.3133384</v>
+        <v>32.6464656</v>
       </c>
       <c r="N99">
-        <v>-15.7033384</v>
+        <v>-16.0364656</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-15.7033384</v>
+        <v>-16.0364656</v>
       </c>
       <c r="Q99">
-        <v>-14.0133384</v>
+        <v>-14.3464656</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.096618401980543</v>
+        <v>3.122027602970815</v>
       </c>
       <c r="T99">
-        <v>17.5668668943779</v>
+        <v>26.35030034156685</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5140292158732815</v>
+        <v>0.508784019792942</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9582,22 +9582,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2592245520594164</v>
+        <v>0.2607745520594164</v>
       </c>
       <c r="C100">
-        <v>-87.78251044728802</v>
+        <v>-89.87177955544689</v>
       </c>
       <c r="D100">
-        <v>69.68948955271198</v>
+        <v>69.25922044455312</v>
       </c>
       <c r="E100">
-        <v>136.282</v>
+        <v>137.941</v>
       </c>
       <c r="F100">
-        <v>162.582</v>
+        <v>164.241</v>
       </c>
       <c r="G100">
         <v>5.11</v>
@@ -9618,28 +9618,28 @@
         <v>16.61</v>
       </c>
       <c r="M100">
-        <v>32.6464656</v>
+        <v>32.97959280000001</v>
       </c>
       <c r="N100">
-        <v>-16.0364656</v>
+        <v>-16.36959280000001</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-16.0364656</v>
+        <v>-16.36959280000001</v>
       </c>
       <c r="Q100">
-        <v>-14.3464656</v>
+        <v>-14.67959280000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.122027602970815</v>
+        <v>6.19825520594163</v>
       </c>
       <c r="T100">
-        <v>26.35030034156685</v>
+        <v>52.70060068313369</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
@@ -9656,91 +9656,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.508784019792942</v>
+        <v>0.5036447872697809</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2607745520594164</v>
-      </c>
-      <c r="C101">
-        <v>-89.87177955544689</v>
-      </c>
-      <c r="D101">
-        <v>69.25922044455312</v>
-      </c>
-      <c r="E101">
-        <v>137.941</v>
-      </c>
-      <c r="F101">
-        <v>164.241</v>
-      </c>
-      <c r="G101">
-        <v>5.11</v>
-      </c>
-      <c r="H101">
-        <v>139.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>18.3</v>
-      </c>
-      <c r="K101">
-        <v>1.69</v>
-      </c>
-      <c r="L101">
-        <v>16.61</v>
-      </c>
-      <c r="M101">
-        <v>32.97959280000001</v>
-      </c>
-      <c r="N101">
-        <v>-16.36959280000001</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-16.36959280000001</v>
-      </c>
-      <c r="Q101">
-        <v>-14.67959280000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.19825520594163</v>
-      </c>
-      <c r="T101">
-        <v>52.70060068313369</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2008</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5036447872697809</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
